--- a/catan_data.xlsx
+++ b/catan_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88b1f18c208c1b3c/Documents/CatanData/catan_data/catan_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="956" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C47A2FE1-F0D0-4FCF-8A3F-D24FF46771D7}"/>
+  <xr:revisionPtr revIDLastSave="1146" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D9A3DB1-114E-4EEC-B0EE-69B4DD8244F7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="15260" xr2:uid="{83B30B11-FE95-4925-9DB4-CCB67C570BD6}"/>
+    <workbookView xWindow="10" yWindow="10" windowWidth="22540" windowHeight="15020" xr2:uid="{83B30B11-FE95-4925-9DB4-CCB67C570BD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1637" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="79">
   <si>
     <t>season</t>
   </si>
@@ -355,10 +355,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
@@ -656,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}">
-  <dimension ref="A1:AP392"/>
+  <dimension ref="A1:AP398"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -38860,7 +38856,7 @@
         <v>31</v>
       </c>
       <c r="L366">
-        <f t="shared" ref="L366:L392" si="9">SUM(O366:V366)</f>
+        <f t="shared" ref="L366:L398" si="9">SUM(O366:V366)</f>
         <v>33</v>
       </c>
       <c r="M366">
@@ -41684,6 +41680,642 @@
       </c>
       <c r="AH392">
         <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A393">
+        <v>2026</v>
+      </c>
+      <c r="B393" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C393">
+        <v>11</v>
+      </c>
+      <c r="D393" t="s">
+        <v>76</v>
+      </c>
+      <c r="E393" t="str">
+        <f>VLOOKUP(D393,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F393" t="s">
+        <v>11</v>
+      </c>
+      <c r="G393">
+        <v>4</v>
+      </c>
+      <c r="H393">
+        <v>0</v>
+      </c>
+      <c r="I393">
+        <v>3</v>
+      </c>
+      <c r="J393" t="s">
+        <v>36</v>
+      </c>
+      <c r="K393" t="s">
+        <v>31</v>
+      </c>
+      <c r="L393">
+        <f t="shared" si="9"/>
+        <v>29</v>
+      </c>
+      <c r="M393">
+        <v>5</v>
+      </c>
+      <c r="N393">
+        <v>4</v>
+      </c>
+      <c r="O393">
+        <v>7</v>
+      </c>
+      <c r="P393">
+        <v>5</v>
+      </c>
+      <c r="Q393">
+        <v>4</v>
+      </c>
+      <c r="R393">
+        <v>4</v>
+      </c>
+      <c r="S393">
+        <v>0</v>
+      </c>
+      <c r="T393">
+        <v>7</v>
+      </c>
+      <c r="U393">
+        <v>0</v>
+      </c>
+      <c r="V393">
+        <v>2</v>
+      </c>
+      <c r="W393">
+        <v>0</v>
+      </c>
+      <c r="X393">
+        <v>0</v>
+      </c>
+      <c r="Y393">
+        <v>0</v>
+      </c>
+      <c r="Z393">
+        <v>0</v>
+      </c>
+      <c r="AA393">
+        <v>0</v>
+      </c>
+      <c r="AB393">
+        <v>0</v>
+      </c>
+      <c r="AC393">
+        <v>0</v>
+      </c>
+      <c r="AD393">
+        <v>0</v>
+      </c>
+      <c r="AE393">
+        <v>0</v>
+      </c>
+      <c r="AF393">
+        <v>0</v>
+      </c>
+      <c r="AG393">
+        <v>0</v>
+      </c>
+      <c r="AH393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A394">
+        <v>2026</v>
+      </c>
+      <c r="B394" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C394">
+        <v>11</v>
+      </c>
+      <c r="D394" t="s">
+        <v>76</v>
+      </c>
+      <c r="E394" t="str">
+        <f>VLOOKUP(D394,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F394" t="s">
+        <v>12</v>
+      </c>
+      <c r="G394">
+        <v>13</v>
+      </c>
+      <c r="H394">
+        <v>6</v>
+      </c>
+      <c r="I394">
+        <v>1</v>
+      </c>
+      <c r="J394" t="s">
+        <v>32</v>
+      </c>
+      <c r="K394" t="s">
+        <v>31</v>
+      </c>
+      <c r="L394">
+        <f t="shared" si="9"/>
+        <v>29</v>
+      </c>
+      <c r="M394">
+        <v>4</v>
+      </c>
+      <c r="N394">
+        <v>3</v>
+      </c>
+      <c r="O394">
+        <v>0</v>
+      </c>
+      <c r="P394">
+        <v>3</v>
+      </c>
+      <c r="Q394">
+        <v>0</v>
+      </c>
+      <c r="R394">
+        <v>22</v>
+      </c>
+      <c r="S394">
+        <v>4</v>
+      </c>
+      <c r="T394">
+        <v>0</v>
+      </c>
+      <c r="U394">
+        <v>0</v>
+      </c>
+      <c r="V394">
+        <v>0</v>
+      </c>
+      <c r="W394">
+        <v>0</v>
+      </c>
+      <c r="X394">
+        <v>0</v>
+      </c>
+      <c r="Y394">
+        <v>0</v>
+      </c>
+      <c r="Z394">
+        <v>1</v>
+      </c>
+      <c r="AA394">
+        <v>0</v>
+      </c>
+      <c r="AB394">
+        <v>0</v>
+      </c>
+      <c r="AC394">
+        <v>0</v>
+      </c>
+      <c r="AD394">
+        <v>0</v>
+      </c>
+      <c r="AE394">
+        <v>0</v>
+      </c>
+      <c r="AF394">
+        <v>0</v>
+      </c>
+      <c r="AG394">
+        <v>0</v>
+      </c>
+      <c r="AH394">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A395">
+        <v>2026</v>
+      </c>
+      <c r="B395" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C395">
+        <v>11</v>
+      </c>
+      <c r="D395" t="s">
+        <v>76</v>
+      </c>
+      <c r="E395" t="str">
+        <f>VLOOKUP(D395,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F395" t="s">
+        <v>13</v>
+      </c>
+      <c r="G395">
+        <v>6</v>
+      </c>
+      <c r="H395">
+        <v>1</v>
+      </c>
+      <c r="I395">
+        <v>2</v>
+      </c>
+      <c r="J395" t="s">
+        <v>37</v>
+      </c>
+      <c r="K395" t="s">
+        <v>31</v>
+      </c>
+      <c r="L395">
+        <f t="shared" si="9"/>
+        <v>33</v>
+      </c>
+      <c r="M395">
+        <v>6</v>
+      </c>
+      <c r="N395">
+        <v>5</v>
+      </c>
+      <c r="O395">
+        <v>7</v>
+      </c>
+      <c r="P395">
+        <v>3</v>
+      </c>
+      <c r="Q395">
+        <v>5</v>
+      </c>
+      <c r="R395">
+        <v>5</v>
+      </c>
+      <c r="S395">
+        <v>2</v>
+      </c>
+      <c r="T395">
+        <v>4</v>
+      </c>
+      <c r="U395">
+        <v>2</v>
+      </c>
+      <c r="V395">
+        <v>5</v>
+      </c>
+      <c r="W395">
+        <v>0</v>
+      </c>
+      <c r="X395">
+        <v>0</v>
+      </c>
+      <c r="Y395">
+        <v>0</v>
+      </c>
+      <c r="Z395">
+        <v>0</v>
+      </c>
+      <c r="AA395">
+        <v>0</v>
+      </c>
+      <c r="AB395">
+        <v>0</v>
+      </c>
+      <c r="AC395">
+        <v>0</v>
+      </c>
+      <c r="AD395">
+        <v>0</v>
+      </c>
+      <c r="AE395">
+        <v>1</v>
+      </c>
+      <c r="AF395">
+        <v>0</v>
+      </c>
+      <c r="AG395">
+        <v>0</v>
+      </c>
+      <c r="AH395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A396">
+        <v>2026</v>
+      </c>
+      <c r="B396" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C396">
+        <v>12</v>
+      </c>
+      <c r="D396" t="s">
+        <v>76</v>
+      </c>
+      <c r="E396" t="str">
+        <f>VLOOKUP(D396,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F396" t="s">
+        <v>12</v>
+      </c>
+      <c r="G396">
+        <v>5</v>
+      </c>
+      <c r="H396">
+        <v>0</v>
+      </c>
+      <c r="I396">
+        <v>3</v>
+      </c>
+      <c r="J396" t="s">
+        <v>36</v>
+      </c>
+      <c r="K396" t="s">
+        <v>31</v>
+      </c>
+      <c r="L396">
+        <f t="shared" si="9"/>
+        <v>33</v>
+      </c>
+      <c r="M396">
+        <v>5</v>
+      </c>
+      <c r="N396">
+        <v>4</v>
+      </c>
+      <c r="O396">
+        <v>9</v>
+      </c>
+      <c r="P396">
+        <v>3</v>
+      </c>
+      <c r="Q396">
+        <v>0</v>
+      </c>
+      <c r="R396">
+        <v>4</v>
+      </c>
+      <c r="S396">
+        <v>6</v>
+      </c>
+      <c r="T396">
+        <v>5</v>
+      </c>
+      <c r="U396">
+        <v>6</v>
+      </c>
+      <c r="V396">
+        <v>0</v>
+      </c>
+      <c r="W396">
+        <v>0</v>
+      </c>
+      <c r="X396">
+        <v>0</v>
+      </c>
+      <c r="Y396">
+        <v>0</v>
+      </c>
+      <c r="Z396">
+        <v>0</v>
+      </c>
+      <c r="AA396">
+        <v>0</v>
+      </c>
+      <c r="AB396">
+        <v>0</v>
+      </c>
+      <c r="AC396">
+        <v>0</v>
+      </c>
+      <c r="AD396">
+        <v>1</v>
+      </c>
+      <c r="AE396">
+        <v>0</v>
+      </c>
+      <c r="AF396">
+        <v>0</v>
+      </c>
+      <c r="AG396">
+        <v>0</v>
+      </c>
+      <c r="AH396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A397">
+        <v>2026</v>
+      </c>
+      <c r="B397" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C397">
+        <v>12</v>
+      </c>
+      <c r="D397" t="s">
+        <v>76</v>
+      </c>
+      <c r="E397" t="str">
+        <f>VLOOKUP(D397,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F397" t="s">
+        <v>13</v>
+      </c>
+      <c r="G397">
+        <v>12</v>
+      </c>
+      <c r="H397">
+        <v>7</v>
+      </c>
+      <c r="I397">
+        <v>2</v>
+      </c>
+      <c r="J397" t="s">
+        <v>32</v>
+      </c>
+      <c r="K397" t="s">
+        <v>31</v>
+      </c>
+      <c r="L397">
+        <f t="shared" si="9"/>
+        <v>36</v>
+      </c>
+      <c r="M397">
+        <v>5</v>
+      </c>
+      <c r="N397">
+        <v>3</v>
+      </c>
+      <c r="O397">
+        <v>10</v>
+      </c>
+      <c r="P397">
+        <v>0</v>
+      </c>
+      <c r="Q397">
+        <v>10</v>
+      </c>
+      <c r="R397">
+        <v>0</v>
+      </c>
+      <c r="S397">
+        <v>4</v>
+      </c>
+      <c r="T397">
+        <v>7</v>
+      </c>
+      <c r="U397">
+        <v>0</v>
+      </c>
+      <c r="V397">
+        <v>5</v>
+      </c>
+      <c r="W397">
+        <v>0</v>
+      </c>
+      <c r="X397">
+        <v>0</v>
+      </c>
+      <c r="Y397">
+        <v>0</v>
+      </c>
+      <c r="Z397">
+        <v>0</v>
+      </c>
+      <c r="AA397">
+        <v>0</v>
+      </c>
+      <c r="AB397">
+        <v>0</v>
+      </c>
+      <c r="AC397">
+        <v>1</v>
+      </c>
+      <c r="AD397">
+        <v>0</v>
+      </c>
+      <c r="AE397">
+        <v>0</v>
+      </c>
+      <c r="AF397">
+        <v>0</v>
+      </c>
+      <c r="AG397">
+        <v>0</v>
+      </c>
+      <c r="AH397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A398">
+        <v>2026</v>
+      </c>
+      <c r="B398" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C398">
+        <v>12</v>
+      </c>
+      <c r="D398" t="s">
+        <v>76</v>
+      </c>
+      <c r="E398" t="str">
+        <f>VLOOKUP(D398,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F398" t="s">
+        <v>11</v>
+      </c>
+      <c r="G398">
+        <v>13</v>
+      </c>
+      <c r="H398">
+        <v>5</v>
+      </c>
+      <c r="I398">
+        <v>1</v>
+      </c>
+      <c r="J398" t="s">
+        <v>37</v>
+      </c>
+      <c r="K398" t="s">
+        <v>31</v>
+      </c>
+      <c r="L398">
+        <f t="shared" si="9"/>
+        <v>35</v>
+      </c>
+      <c r="M398">
+        <v>5</v>
+      </c>
+      <c r="N398">
+        <v>5</v>
+      </c>
+      <c r="O398">
+        <v>5</v>
+      </c>
+      <c r="P398">
+        <v>8</v>
+      </c>
+      <c r="Q398">
+        <v>4</v>
+      </c>
+      <c r="R398">
+        <v>3</v>
+      </c>
+      <c r="S398">
+        <v>3</v>
+      </c>
+      <c r="T398">
+        <v>5</v>
+      </c>
+      <c r="U398">
+        <v>3</v>
+      </c>
+      <c r="V398">
+        <v>4</v>
+      </c>
+      <c r="W398">
+        <v>0</v>
+      </c>
+      <c r="X398">
+        <v>0</v>
+      </c>
+      <c r="Y398">
+        <v>0</v>
+      </c>
+      <c r="Z398">
+        <v>0</v>
+      </c>
+      <c r="AA398">
+        <v>0</v>
+      </c>
+      <c r="AB398">
+        <v>0</v>
+      </c>
+      <c r="AC398">
+        <v>0</v>
+      </c>
+      <c r="AD398">
+        <v>0</v>
+      </c>
+      <c r="AE398">
+        <v>0</v>
+      </c>
+      <c r="AF398">
+        <v>0</v>
+      </c>
+      <c r="AG398">
+        <v>0</v>
+      </c>
+      <c r="AH398">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/catan_data.xlsx
+++ b/catan_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88b1f18c208c1b3c/Documents/CatanData/catan_data/catan_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1146" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D9A3DB1-114E-4EEC-B0EE-69B4DD8244F7}"/>
+  <xr:revisionPtr revIDLastSave="1434" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD78A930-CC68-458A-AA1A-EE0166F014F2}"/>
   <bookViews>
     <workbookView xWindow="10" yWindow="10" windowWidth="22540" windowHeight="15020" xr2:uid="{83B30B11-FE95-4925-9DB4-CCB67C570BD6}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$AP$389</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$AP$407</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1697" uniqueCount="79">
   <si>
     <t>season</t>
   </si>
@@ -355,6 +355,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
@@ -652,7 +656,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}">
-  <dimension ref="A1:AP398"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:AP407"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -843,7 +848,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2022</v>
       </c>
@@ -946,7 +951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2022</v>
       </c>
@@ -1049,7 +1054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2022</v>
       </c>
@@ -1152,7 +1157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2022</v>
       </c>
@@ -1255,7 +1260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2022</v>
       </c>
@@ -1358,7 +1363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2022</v>
       </c>
@@ -1461,7 +1466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2022</v>
       </c>
@@ -1564,7 +1569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2022</v>
       </c>
@@ -1667,7 +1672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2022</v>
       </c>
@@ -1770,7 +1775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2022</v>
       </c>
@@ -1873,7 +1878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2022</v>
       </c>
@@ -1976,7 +1981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2022</v>
       </c>
@@ -2079,7 +2084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2022</v>
       </c>
@@ -2182,7 +2187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2022</v>
       </c>
@@ -2285,7 +2290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2022</v>
       </c>
@@ -2388,7 +2393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2022</v>
       </c>
@@ -2491,7 +2496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2022</v>
       </c>
@@ -2594,7 +2599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2022</v>
       </c>
@@ -2697,7 +2702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2022</v>
       </c>
@@ -2800,7 +2805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2022</v>
       </c>
@@ -2903,7 +2908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2022</v>
       </c>
@@ -3315,7 +3320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2022</v>
       </c>
@@ -3421,7 +3426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2022</v>
       </c>
@@ -3527,7 +3532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2022</v>
       </c>
@@ -3951,7 +3956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>2022</v>
       </c>
@@ -4057,7 +4062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>2022</v>
       </c>
@@ -4163,7 +4168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>2022</v>
       </c>
@@ -4269,7 +4274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>2022</v>
       </c>
@@ -4375,7 +4380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>2022</v>
       </c>
@@ -4481,7 +4486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>2022</v>
       </c>
@@ -4587,7 +4592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>2022</v>
       </c>
@@ -4693,7 +4698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>2022</v>
       </c>
@@ -4799,7 +4804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>2022</v>
       </c>
@@ -4905,7 +4910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>2022</v>
       </c>
@@ -5011,7 +5016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>2022</v>
       </c>
@@ -5117,7 +5122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>2022</v>
       </c>
@@ -5223,7 +5228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>2022</v>
       </c>
@@ -5329,7 +5334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>2022</v>
       </c>
@@ -5435,7 +5440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>2022</v>
       </c>
@@ -5859,7 +5864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>2022</v>
       </c>
@@ -5965,7 +5970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>2022</v>
       </c>
@@ -6071,7 +6076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>2022</v>
       </c>
@@ -6813,7 +6818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>2022</v>
       </c>
@@ -6919,7 +6924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>2022</v>
       </c>
@@ -7025,7 +7030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>2022</v>
       </c>
@@ -7131,7 +7136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>2022</v>
       </c>
@@ -7237,7 +7242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>2022</v>
       </c>
@@ -7343,7 +7348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>2022</v>
       </c>
@@ -7449,7 +7454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>2022</v>
       </c>
@@ -7555,7 +7560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>2022</v>
       </c>
@@ -7661,7 +7666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>2022</v>
       </c>
@@ -7767,7 +7772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>2022</v>
       </c>
@@ -7873,7 +7878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>2022</v>
       </c>
@@ -7979,7 +7984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>2022</v>
       </c>
@@ -8085,7 +8090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>2022</v>
       </c>
@@ -8191,7 +8196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>2022</v>
       </c>
@@ -8297,7 +8302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>2022</v>
       </c>
@@ -8721,7 +8726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>2022</v>
       </c>
@@ -8827,7 +8832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>2022</v>
       </c>
@@ -8933,7 +8938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>2022</v>
       </c>
@@ -9039,7 +9044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>2022</v>
       </c>
@@ -9075,7 +9080,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>2022</v>
       </c>
@@ -9111,7 +9116,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="83" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>2022</v>
       </c>
@@ -9147,7 +9152,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="84" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>2022</v>
       </c>
@@ -9253,7 +9258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>2022</v>
       </c>
@@ -9359,7 +9364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>2022</v>
       </c>
@@ -9465,7 +9470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>2022</v>
       </c>
@@ -9571,7 +9576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>2022</v>
       </c>
@@ -9677,7 +9682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>2022</v>
       </c>
@@ -9783,7 +9788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>2022</v>
       </c>
@@ -9889,7 +9894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>2022</v>
       </c>
@@ -9995,7 +10000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>2022</v>
       </c>
@@ -10737,7 +10742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>2023</v>
       </c>
@@ -10843,7 +10848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>2023</v>
       </c>
@@ -10949,7 +10954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>2023</v>
       </c>
@@ -11055,7 +11060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>2023</v>
       </c>
@@ -11161,7 +11166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>2023</v>
       </c>
@@ -11267,7 +11272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>2023</v>
       </c>
@@ -12009,7 +12014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>2023</v>
       </c>
@@ -12115,7 +12120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>2023</v>
       </c>
@@ -12221,7 +12226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>2023</v>
       </c>
@@ -12327,7 +12332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>2023</v>
       </c>
@@ -12433,7 +12438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>2023</v>
       </c>
@@ -12539,7 +12544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>2023</v>
       </c>
@@ -12963,7 +12968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>2023</v>
       </c>
@@ -12996,7 +13001,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="121" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>2023</v>
       </c>
@@ -13029,7 +13034,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="122" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>2023</v>
       </c>
@@ -13062,7 +13067,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="123" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>2023</v>
       </c>
@@ -13168,7 +13173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>2023</v>
       </c>
@@ -13274,7 +13279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>2023</v>
       </c>
@@ -13698,7 +13703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>2023</v>
       </c>
@@ -13804,7 +13809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>2023</v>
       </c>
@@ -13910,7 +13915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>2023</v>
       </c>
@@ -14970,7 +14975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>2023</v>
       </c>
@@ -15076,7 +15081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>2023</v>
       </c>
@@ -15182,7 +15187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>2023</v>
       </c>
@@ -15924,7 +15929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>2023</v>
       </c>
@@ -16030,7 +16035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>2023</v>
       </c>
@@ -16136,7 +16141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>2023</v>
       </c>
@@ -16878,7 +16883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>2024</v>
       </c>
@@ -16984,7 +16989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>2024</v>
       </c>
@@ -17090,7 +17095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>2024</v>
       </c>
@@ -17832,7 +17837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>2024</v>
       </c>
@@ -17938,7 +17943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>2024</v>
       </c>
@@ -18044,7 +18049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>2024</v>
       </c>
@@ -18150,7 +18155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>2024</v>
       </c>
@@ -18256,7 +18261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>2024</v>
       </c>
@@ -18362,7 +18367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>2024</v>
       </c>
@@ -18468,7 +18473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>2024</v>
       </c>
@@ -18574,7 +18579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>2024</v>
       </c>
@@ -18680,7 +18685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>2024</v>
       </c>
@@ -18786,7 +18791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>2024</v>
       </c>
@@ -18892,7 +18897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>2024</v>
       </c>
@@ -18998,7 +19003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>2024</v>
       </c>
@@ -19422,7 +19427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>2024</v>
       </c>
@@ -19528,7 +19533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>2024</v>
       </c>
@@ -19634,7 +19639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>2024</v>
       </c>
@@ -20058,7 +20063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>2024</v>
       </c>
@@ -20164,7 +20169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>2024</v>
       </c>
@@ -20270,7 +20275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>2024</v>
       </c>
@@ -20376,7 +20381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>2024</v>
       </c>
@@ -20482,7 +20487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>2024</v>
       </c>
@@ -20588,7 +20593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>2024</v>
       </c>
@@ -21012,7 +21017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>2024</v>
       </c>
@@ -21118,7 +21123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>2024</v>
       </c>
@@ -21224,7 +21229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>2024</v>
       </c>
@@ -21648,7 +21653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>2024</v>
       </c>
@@ -21754,7 +21759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>2024</v>
       </c>
@@ -21860,7 +21865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>2024</v>
       </c>
@@ -21966,7 +21971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>2024</v>
       </c>
@@ -22072,7 +22077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>2024</v>
       </c>
@@ -22178,7 +22183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>2024</v>
       </c>
@@ -22284,7 +22289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>2024</v>
       </c>
@@ -22390,7 +22395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>2024</v>
       </c>
@@ -22496,7 +22501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>2024</v>
       </c>
@@ -22920,7 +22925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>2024</v>
       </c>
@@ -23026,7 +23031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>2024</v>
       </c>
@@ -23132,7 +23137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>2024</v>
       </c>
@@ -23874,7 +23879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>2024</v>
       </c>
@@ -23980,7 +23985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>2024</v>
       </c>
@@ -24086,7 +24091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>2024</v>
       </c>
@@ -24192,7 +24197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>2024</v>
       </c>
@@ -24298,7 +24303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>2024</v>
       </c>
@@ -24404,7 +24409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>2024</v>
       </c>
@@ -24828,7 +24833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>2024</v>
       </c>
@@ -24934,7 +24939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>2024</v>
       </c>
@@ -25040,7 +25045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>2024</v>
       </c>
@@ -25464,7 +25469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240">
         <v>2024</v>
       </c>
@@ -25570,7 +25575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241">
         <v>2024</v>
       </c>
@@ -25676,7 +25681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242">
         <v>2024</v>
       </c>
@@ -25782,7 +25787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243">
         <v>2024</v>
       </c>
@@ -25888,7 +25893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244">
         <v>2024</v>
       </c>
@@ -25994,7 +25999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245">
         <v>2024</v>
       </c>
@@ -26100,7 +26105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246">
         <v>2024</v>
       </c>
@@ -26206,7 +26211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247">
         <v>2024</v>
       </c>
@@ -26312,7 +26317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248">
         <v>2024</v>
       </c>
@@ -26418,7 +26423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249">
         <v>2024</v>
       </c>
@@ -26524,7 +26529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250">
         <v>2024</v>
       </c>
@@ -26630,7 +26635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251">
         <v>2024</v>
       </c>
@@ -26736,7 +26741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252">
         <v>2024</v>
       </c>
@@ -26842,7 +26847,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="253" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253">
         <v>2024</v>
       </c>
@@ -26948,7 +26953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254">
         <v>2024</v>
       </c>
@@ -27054,7 +27059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255">
         <v>2024</v>
       </c>
@@ -27160,7 +27165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256">
         <v>2024</v>
       </c>
@@ -27266,7 +27271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257">
         <v>2024</v>
       </c>
@@ -27372,7 +27377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258">
         <v>2024</v>
       </c>
@@ -27478,7 +27483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259">
         <v>2024</v>
       </c>
@@ -27584,7 +27589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260">
         <v>2024</v>
       </c>
@@ -27690,7 +27695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261">
         <v>2024</v>
       </c>
@@ -27796,7 +27801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262">
         <v>2024</v>
       </c>
@@ -27902,7 +27907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263">
         <v>2024</v>
       </c>
@@ -28326,7 +28331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267">
         <v>2024</v>
       </c>
@@ -28432,7 +28437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268">
         <v>2024</v>
       </c>
@@ -28538,7 +28543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269">
         <v>2024</v>
       </c>
@@ -28644,7 +28649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270">
         <v>2024</v>
       </c>
@@ -28750,7 +28755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271">
         <v>2024</v>
       </c>
@@ -28856,7 +28861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272">
         <v>2024</v>
       </c>
@@ -28962,7 +28967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273">
         <v>2024</v>
       </c>
@@ -29068,7 +29073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274">
         <v>2024</v>
       </c>
@@ -29174,7 +29179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275">
         <v>2024</v>
       </c>
@@ -29280,7 +29285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276">
         <v>2024</v>
       </c>
@@ -29386,7 +29391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277">
         <v>2024</v>
       </c>
@@ -29492,7 +29497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278">
         <v>2024</v>
       </c>
@@ -29598,7 +29603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279">
         <v>2024</v>
       </c>
@@ -29704,7 +29709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280">
         <v>2024</v>
       </c>
@@ -29810,7 +29815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281">
         <v>2024</v>
       </c>
@@ -29916,7 +29921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282">
         <v>2024</v>
       </c>
@@ -30022,7 +30027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283">
         <v>2024</v>
       </c>
@@ -30128,7 +30133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284">
         <v>2024</v>
       </c>
@@ -30234,7 +30239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285">
         <v>2024</v>
       </c>
@@ -30340,7 +30345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286">
         <v>2024</v>
       </c>
@@ -30446,7 +30451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287">
         <v>2024</v>
       </c>
@@ -30552,7 +30557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288">
         <v>2024</v>
       </c>
@@ -30658,7 +30663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289">
         <v>2024</v>
       </c>
@@ -30764,7 +30769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290">
         <v>2024</v>
       </c>
@@ -30870,7 +30875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291">
         <v>2024</v>
       </c>
@@ -30976,7 +30981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292">
         <v>2024</v>
       </c>
@@ -31082,7 +31087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293">
         <v>2024</v>
       </c>
@@ -31506,7 +31511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297">
         <v>2025</v>
       </c>
@@ -31612,7 +31617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298">
         <v>2025</v>
       </c>
@@ -31718,7 +31723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299">
         <v>2025</v>
       </c>
@@ -31824,7 +31829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300">
         <v>2025</v>
       </c>
@@ -31930,7 +31935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301">
         <v>2025</v>
       </c>
@@ -32036,7 +32041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302">
         <v>2025</v>
       </c>
@@ -32142,7 +32147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303">
         <v>2025</v>
       </c>
@@ -32248,7 +32253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304">
         <v>2025</v>
       </c>
@@ -32354,7 +32359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305">
         <v>2025</v>
       </c>
@@ -32460,7 +32465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306">
         <v>2025</v>
       </c>
@@ -32566,7 +32571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307">
         <v>2025</v>
       </c>
@@ -32672,7 +32677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308">
         <v>2025</v>
       </c>
@@ -32778,7 +32783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309">
         <v>2025</v>
       </c>
@@ -32884,7 +32889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310">
         <v>2025</v>
       </c>
@@ -32990,7 +32995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311">
         <v>2025</v>
       </c>
@@ -33096,7 +33101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312">
         <v>2025</v>
       </c>
@@ -33202,7 +33207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313">
         <v>2025</v>
       </c>
@@ -33308,7 +33313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314">
         <v>2025</v>
       </c>
@@ -33414,7 +33419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315">
         <v>2025</v>
       </c>
@@ -33520,7 +33525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316">
         <v>2025</v>
       </c>
@@ -33626,7 +33631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317">
         <v>2025</v>
       </c>
@@ -34050,7 +34055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321">
         <v>2025</v>
       </c>
@@ -34156,7 +34161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322">
         <v>2025</v>
       </c>
@@ -34262,7 +34267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323">
         <v>2025</v>
       </c>
@@ -34368,7 +34373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324">
         <v>2025</v>
       </c>
@@ -34474,7 +34479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325">
         <v>2025</v>
       </c>
@@ -34580,7 +34585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326">
         <v>2025</v>
       </c>
@@ -34686,7 +34691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327">
         <v>2025</v>
       </c>
@@ -34792,7 +34797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328">
         <v>2025</v>
       </c>
@@ -34898,7 +34903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329">
         <v>2025</v>
       </c>
@@ -35004,7 +35009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330">
         <v>2025</v>
       </c>
@@ -35110,7 +35115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331">
         <v>2025</v>
       </c>
@@ -35216,7 +35221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332">
         <v>2025</v>
       </c>
@@ -35640,7 +35645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336">
         <v>2025</v>
       </c>
@@ -35746,7 +35751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337">
         <v>2025</v>
       </c>
@@ -35852,7 +35857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338">
         <v>2025</v>
       </c>
@@ -35958,7 +35963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339">
         <v>2025</v>
       </c>
@@ -36064,7 +36069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340">
         <v>2025</v>
       </c>
@@ -36170,7 +36175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341">
         <v>2025</v>
       </c>
@@ -36276,7 +36281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342">
         <v>2025</v>
       </c>
@@ -36382,7 +36387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343">
         <v>2025</v>
       </c>
@@ -36488,7 +36493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344">
         <v>2025</v>
       </c>
@@ -36594,7 +36599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345">
         <v>2025</v>
       </c>
@@ -36700,7 +36705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346">
         <v>2025</v>
       </c>
@@ -36806,7 +36811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347">
         <v>2025</v>
       </c>
@@ -36912,7 +36917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348">
         <v>2025</v>
       </c>
@@ -37018,7 +37023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349">
         <v>2025</v>
       </c>
@@ -37124,7 +37129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350">
         <v>2025</v>
       </c>
@@ -37230,7 +37235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351">
         <v>2025</v>
       </c>
@@ -37336,7 +37341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352">
         <v>2025</v>
       </c>
@@ -37442,7 +37447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353">
         <v>2025</v>
       </c>
@@ -37548,7 +37553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354">
         <v>2025</v>
       </c>
@@ -37654,7 +37659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355">
         <v>2025</v>
       </c>
@@ -37760,7 +37765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356">
         <v>2025</v>
       </c>
@@ -37866,7 +37871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357">
         <v>2025</v>
       </c>
@@ -37972,7 +37977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358">
         <v>2025</v>
       </c>
@@ -38078,7 +38083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359">
         <v>2025</v>
       </c>
@@ -38184,7 +38189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360">
         <v>2025</v>
       </c>
@@ -38290,7 +38295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361">
         <v>2025</v>
       </c>
@@ -38396,7 +38401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362">
         <v>2025</v>
       </c>
@@ -38502,7 +38507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363">
         <v>2026</v>
       </c>
@@ -38608,7 +38613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364">
         <v>2026</v>
       </c>
@@ -38714,7 +38719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365">
         <v>2026</v>
       </c>
@@ -38820,7 +38825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="366" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366">
         <v>2026</v>
       </c>
@@ -38856,7 +38861,7 @@
         <v>31</v>
       </c>
       <c r="L366">
-        <f t="shared" ref="L366:L398" si="9">SUM(O366:V366)</f>
+        <f t="shared" ref="L366:L407" si="9">SUM(O366:V366)</f>
         <v>33</v>
       </c>
       <c r="M366">
@@ -38926,7 +38931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367">
         <v>2026</v>
       </c>
@@ -39032,7 +39037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368">
         <v>2026</v>
       </c>
@@ -39138,7 +39143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="369" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369">
         <v>2026</v>
       </c>
@@ -39244,7 +39249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370">
         <v>2026</v>
       </c>
@@ -39350,7 +39355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A371">
         <v>2026</v>
       </c>
@@ -39456,7 +39461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372">
         <v>2026</v>
       </c>
@@ -39562,7 +39567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="373" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373">
         <v>2026</v>
       </c>
@@ -39668,7 +39673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374">
         <v>2026</v>
       </c>
@@ -39774,7 +39779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="375" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A375">
         <v>2026</v>
       </c>
@@ -39880,7 +39885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376">
         <v>2026</v>
       </c>
@@ -39986,7 +39991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377">
         <v>2026</v>
       </c>
@@ -40092,7 +40097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378">
         <v>2026</v>
       </c>
@@ -40198,7 +40203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="379" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379">
         <v>2026</v>
       </c>
@@ -40304,7 +40309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380">
         <v>2026</v>
       </c>
@@ -40410,7 +40415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381">
         <v>2026</v>
       </c>
@@ -40516,7 +40521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="382" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382">
         <v>2026</v>
       </c>
@@ -40622,7 +40627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="383" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383">
         <v>2026</v>
       </c>
@@ -40728,7 +40733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384">
         <v>2026</v>
       </c>
@@ -40834,7 +40839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A385">
         <v>2026</v>
       </c>
@@ -40940,7 +40945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386">
         <v>2026</v>
       </c>
@@ -41046,7 +41051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A387">
         <v>2026</v>
       </c>
@@ -41152,7 +41157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A388">
         <v>2026</v>
       </c>
@@ -41258,7 +41263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A389">
         <v>2026</v>
       </c>
@@ -41364,7 +41369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A390">
         <v>2026</v>
       </c>
@@ -41470,7 +41475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A391">
         <v>2026</v>
       </c>
@@ -41576,7 +41581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A392">
         <v>2026</v>
       </c>
@@ -41682,7 +41687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A393">
         <v>2026</v>
       </c>
@@ -41788,7 +41793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A394">
         <v>2026</v>
       </c>
@@ -41894,7 +41899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395">
         <v>2026</v>
       </c>
@@ -42000,7 +42005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A396">
         <v>2026</v>
       </c>
@@ -42106,7 +42111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A397">
         <v>2026</v>
       </c>
@@ -42212,7 +42217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="A398">
         <v>2026</v>
       </c>
@@ -42318,8 +42323,968 @@
         <v>1</v>
       </c>
     </row>
+    <row r="399" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A399">
+        <v>2026</v>
+      </c>
+      <c r="B399" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C399">
+        <v>13</v>
+      </c>
+      <c r="D399" t="s">
+        <v>76</v>
+      </c>
+      <c r="E399" t="str">
+        <f>VLOOKUP(D399,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F399" t="s">
+        <v>11</v>
+      </c>
+      <c r="G399">
+        <v>9</v>
+      </c>
+      <c r="H399">
+        <v>2</v>
+      </c>
+      <c r="I399">
+        <v>2</v>
+      </c>
+      <c r="J399" t="s">
+        <v>36</v>
+      </c>
+      <c r="K399" t="s">
+        <v>31</v>
+      </c>
+      <c r="L399">
+        <f t="shared" si="9"/>
+        <v>31</v>
+      </c>
+      <c r="M399">
+        <v>6</v>
+      </c>
+      <c r="N399">
+        <v>4</v>
+      </c>
+      <c r="O399">
+        <v>0</v>
+      </c>
+      <c r="P399">
+        <v>3</v>
+      </c>
+      <c r="Q399">
+        <v>5</v>
+      </c>
+      <c r="R399">
+        <v>9</v>
+      </c>
+      <c r="S399">
+        <v>7</v>
+      </c>
+      <c r="T399">
+        <v>0</v>
+      </c>
+      <c r="U399">
+        <v>2</v>
+      </c>
+      <c r="V399">
+        <v>5</v>
+      </c>
+      <c r="W399">
+        <v>0</v>
+      </c>
+      <c r="X399">
+        <v>0</v>
+      </c>
+      <c r="Y399">
+        <v>0</v>
+      </c>
+      <c r="Z399">
+        <v>0</v>
+      </c>
+      <c r="AA399">
+        <v>0</v>
+      </c>
+      <c r="AB399">
+        <v>0</v>
+      </c>
+      <c r="AC399">
+        <v>0</v>
+      </c>
+      <c r="AD399">
+        <v>0</v>
+      </c>
+      <c r="AE399">
+        <v>0</v>
+      </c>
+      <c r="AF399">
+        <v>0</v>
+      </c>
+      <c r="AG399">
+        <v>1</v>
+      </c>
+      <c r="AH399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A400">
+        <v>2026</v>
+      </c>
+      <c r="B400" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C400">
+        <v>13</v>
+      </c>
+      <c r="D400" t="s">
+        <v>76</v>
+      </c>
+      <c r="E400" t="str">
+        <f>VLOOKUP(D400,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F400" t="s">
+        <v>12</v>
+      </c>
+      <c r="G400">
+        <v>8</v>
+      </c>
+      <c r="H400">
+        <v>2</v>
+      </c>
+      <c r="I400">
+        <v>3</v>
+      </c>
+      <c r="J400" t="s">
+        <v>32</v>
+      </c>
+      <c r="K400" t="s">
+        <v>31</v>
+      </c>
+      <c r="L400">
+        <f t="shared" si="9"/>
+        <v>33</v>
+      </c>
+      <c r="M400">
+        <v>6</v>
+      </c>
+      <c r="N400">
+        <v>4</v>
+      </c>
+      <c r="O400">
+        <v>3</v>
+      </c>
+      <c r="P400">
+        <v>0</v>
+      </c>
+      <c r="Q400">
+        <v>9</v>
+      </c>
+      <c r="R400">
+        <v>4</v>
+      </c>
+      <c r="S400">
+        <v>7</v>
+      </c>
+      <c r="T400">
+        <v>3</v>
+      </c>
+      <c r="U400">
+        <v>7</v>
+      </c>
+      <c r="V400">
+        <v>0</v>
+      </c>
+      <c r="W400">
+        <v>0</v>
+      </c>
+      <c r="X400">
+        <v>0</v>
+      </c>
+      <c r="Y400">
+        <v>0</v>
+      </c>
+      <c r="Z400">
+        <v>0</v>
+      </c>
+      <c r="AA400">
+        <v>0</v>
+      </c>
+      <c r="AB400">
+        <v>0</v>
+      </c>
+      <c r="AC400">
+        <v>0</v>
+      </c>
+      <c r="AD400">
+        <v>0</v>
+      </c>
+      <c r="AE400">
+        <v>0</v>
+      </c>
+      <c r="AF400">
+        <v>1</v>
+      </c>
+      <c r="AG400">
+        <v>0</v>
+      </c>
+      <c r="AH400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A401">
+        <v>2026</v>
+      </c>
+      <c r="B401" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C401">
+        <v>13</v>
+      </c>
+      <c r="D401" t="s">
+        <v>76</v>
+      </c>
+      <c r="E401" t="str">
+        <f>VLOOKUP(D401,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F401" t="s">
+        <v>13</v>
+      </c>
+      <c r="G401">
+        <v>13</v>
+      </c>
+      <c r="H401">
+        <v>6</v>
+      </c>
+      <c r="I401">
+        <v>1</v>
+      </c>
+      <c r="J401" t="s">
+        <v>37</v>
+      </c>
+      <c r="K401" t="s">
+        <v>31</v>
+      </c>
+      <c r="L401">
+        <f t="shared" si="9"/>
+        <v>34</v>
+      </c>
+      <c r="M401">
+        <v>6</v>
+      </c>
+      <c r="N401">
+        <v>4</v>
+      </c>
+      <c r="O401">
+        <v>10</v>
+      </c>
+      <c r="P401">
+        <v>4</v>
+      </c>
+      <c r="Q401">
+        <v>3</v>
+      </c>
+      <c r="R401">
+        <v>5</v>
+      </c>
+      <c r="S401">
+        <v>0</v>
+      </c>
+      <c r="T401">
+        <v>9</v>
+      </c>
+      <c r="U401">
+        <v>0</v>
+      </c>
+      <c r="V401">
+        <v>3</v>
+      </c>
+      <c r="W401">
+        <v>0</v>
+      </c>
+      <c r="X401">
+        <v>0</v>
+      </c>
+      <c r="Y401">
+        <v>0</v>
+      </c>
+      <c r="Z401">
+        <v>0</v>
+      </c>
+      <c r="AA401">
+        <v>0</v>
+      </c>
+      <c r="AB401">
+        <v>0</v>
+      </c>
+      <c r="AC401">
+        <v>0</v>
+      </c>
+      <c r="AD401">
+        <v>1</v>
+      </c>
+      <c r="AE401">
+        <v>1</v>
+      </c>
+      <c r="AF401">
+        <v>0</v>
+      </c>
+      <c r="AG401">
+        <v>0</v>
+      </c>
+      <c r="AH401">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A402">
+        <v>2026</v>
+      </c>
+      <c r="B402" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C402">
+        <v>14</v>
+      </c>
+      <c r="D402" t="s">
+        <v>76</v>
+      </c>
+      <c r="E402" t="str">
+        <f>VLOOKUP(D402,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F402" t="s">
+        <v>13</v>
+      </c>
+      <c r="G402">
+        <v>7</v>
+      </c>
+      <c r="H402">
+        <v>2</v>
+      </c>
+      <c r="I402">
+        <v>3</v>
+      </c>
+      <c r="J402" t="s">
+        <v>36</v>
+      </c>
+      <c r="K402" t="s">
+        <v>31</v>
+      </c>
+      <c r="L402">
+        <f t="shared" si="9"/>
+        <v>33</v>
+      </c>
+      <c r="M402">
+        <v>6</v>
+      </c>
+      <c r="N402">
+        <v>4</v>
+      </c>
+      <c r="O402">
+        <v>9</v>
+      </c>
+      <c r="P402">
+        <v>10</v>
+      </c>
+      <c r="Q402">
+        <v>0</v>
+      </c>
+      <c r="R402">
+        <v>4</v>
+      </c>
+      <c r="S402">
+        <v>5</v>
+      </c>
+      <c r="T402">
+        <v>0</v>
+      </c>
+      <c r="U402">
+        <v>5</v>
+      </c>
+      <c r="V402">
+        <v>0</v>
+      </c>
+      <c r="W402">
+        <v>0</v>
+      </c>
+      <c r="X402">
+        <v>0</v>
+      </c>
+      <c r="Y402">
+        <v>0</v>
+      </c>
+      <c r="Z402">
+        <v>0</v>
+      </c>
+      <c r="AA402">
+        <v>0</v>
+      </c>
+      <c r="AB402">
+        <v>0</v>
+      </c>
+      <c r="AC402">
+        <v>0</v>
+      </c>
+      <c r="AD402">
+        <v>0</v>
+      </c>
+      <c r="AE402">
+        <v>0</v>
+      </c>
+      <c r="AF402">
+        <v>0</v>
+      </c>
+      <c r="AG402">
+        <v>1</v>
+      </c>
+      <c r="AH402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A403">
+        <v>2026</v>
+      </c>
+      <c r="B403" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C403">
+        <v>14</v>
+      </c>
+      <c r="D403" t="s">
+        <v>76</v>
+      </c>
+      <c r="E403" t="str">
+        <f>VLOOKUP(D403,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F403" t="s">
+        <v>12</v>
+      </c>
+      <c r="G403">
+        <v>9</v>
+      </c>
+      <c r="H403">
+        <v>3</v>
+      </c>
+      <c r="I403">
+        <v>2</v>
+      </c>
+      <c r="J403" t="s">
+        <v>32</v>
+      </c>
+      <c r="K403" t="s">
+        <v>31</v>
+      </c>
+      <c r="L403">
+        <f t="shared" si="9"/>
+        <v>30</v>
+      </c>
+      <c r="M403">
+        <v>6</v>
+      </c>
+      <c r="N403">
+        <v>5</v>
+      </c>
+      <c r="O403">
+        <v>5</v>
+      </c>
+      <c r="P403">
+        <v>4</v>
+      </c>
+      <c r="Q403">
+        <v>5</v>
+      </c>
+      <c r="R403">
+        <v>5</v>
+      </c>
+      <c r="S403">
+        <v>2</v>
+      </c>
+      <c r="T403">
+        <v>5</v>
+      </c>
+      <c r="U403">
+        <v>2</v>
+      </c>
+      <c r="V403">
+        <v>2</v>
+      </c>
+      <c r="W403">
+        <v>0</v>
+      </c>
+      <c r="X403">
+        <v>0</v>
+      </c>
+      <c r="Y403">
+        <v>0</v>
+      </c>
+      <c r="Z403">
+        <v>0</v>
+      </c>
+      <c r="AA403">
+        <v>0</v>
+      </c>
+      <c r="AB403">
+        <v>0</v>
+      </c>
+      <c r="AC403">
+        <v>0</v>
+      </c>
+      <c r="AD403">
+        <v>1</v>
+      </c>
+      <c r="AE403">
+        <v>0</v>
+      </c>
+      <c r="AF403">
+        <v>0</v>
+      </c>
+      <c r="AG403">
+        <v>0</v>
+      </c>
+      <c r="AH403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A404">
+        <v>2026</v>
+      </c>
+      <c r="B404" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C404">
+        <v>14</v>
+      </c>
+      <c r="D404" t="s">
+        <v>76</v>
+      </c>
+      <c r="E404" t="str">
+        <f>VLOOKUP(D404,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F404" t="s">
+        <v>11</v>
+      </c>
+      <c r="G404">
+        <v>13</v>
+      </c>
+      <c r="H404">
+        <v>5</v>
+      </c>
+      <c r="I404">
+        <v>1</v>
+      </c>
+      <c r="J404" t="s">
+        <v>37</v>
+      </c>
+      <c r="K404" t="s">
+        <v>31</v>
+      </c>
+      <c r="L404">
+        <f t="shared" si="9"/>
+        <v>36</v>
+      </c>
+      <c r="M404">
+        <v>6</v>
+      </c>
+      <c r="N404">
+        <v>4</v>
+      </c>
+      <c r="O404">
+        <v>4</v>
+      </c>
+      <c r="P404">
+        <v>10</v>
+      </c>
+      <c r="Q404">
+        <v>5</v>
+      </c>
+      <c r="R404">
+        <v>0</v>
+      </c>
+      <c r="S404">
+        <v>8</v>
+      </c>
+      <c r="T404">
+        <v>4</v>
+      </c>
+      <c r="U404">
+        <v>0</v>
+      </c>
+      <c r="V404">
+        <v>5</v>
+      </c>
+      <c r="W404">
+        <v>0</v>
+      </c>
+      <c r="X404">
+        <v>0</v>
+      </c>
+      <c r="Y404">
+        <v>0</v>
+      </c>
+      <c r="Z404">
+        <v>0</v>
+      </c>
+      <c r="AA404">
+        <v>0</v>
+      </c>
+      <c r="AB404">
+        <v>0</v>
+      </c>
+      <c r="AC404">
+        <v>0</v>
+      </c>
+      <c r="AD404">
+        <v>0</v>
+      </c>
+      <c r="AE404">
+        <v>0</v>
+      </c>
+      <c r="AF404">
+        <v>1</v>
+      </c>
+      <c r="AG404">
+        <v>0</v>
+      </c>
+      <c r="AH404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A405">
+        <v>2026</v>
+      </c>
+      <c r="B405" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C405">
+        <v>15</v>
+      </c>
+      <c r="D405" t="s">
+        <v>76</v>
+      </c>
+      <c r="E405" t="str">
+        <f>VLOOKUP(D405,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F405" t="s">
+        <v>13</v>
+      </c>
+      <c r="G405">
+        <v>13</v>
+      </c>
+      <c r="H405">
+        <v>6</v>
+      </c>
+      <c r="I405">
+        <v>1</v>
+      </c>
+      <c r="J405" t="s">
+        <v>36</v>
+      </c>
+      <c r="K405" t="s">
+        <v>32</v>
+      </c>
+      <c r="L405">
+        <f t="shared" si="9"/>
+        <v>34</v>
+      </c>
+      <c r="M405">
+        <v>5</v>
+      </c>
+      <c r="N405">
+        <v>4</v>
+      </c>
+      <c r="O405">
+        <v>8</v>
+      </c>
+      <c r="P405">
+        <v>0</v>
+      </c>
+      <c r="Q405">
+        <v>10</v>
+      </c>
+      <c r="R405">
+        <v>4</v>
+      </c>
+      <c r="S405">
+        <v>2</v>
+      </c>
+      <c r="T405">
+        <v>8</v>
+      </c>
+      <c r="U405">
+        <v>2</v>
+      </c>
+      <c r="V405">
+        <v>0</v>
+      </c>
+      <c r="W405">
+        <v>0</v>
+      </c>
+      <c r="X405">
+        <v>0</v>
+      </c>
+      <c r="Y405">
+        <v>0</v>
+      </c>
+      <c r="Z405">
+        <v>0</v>
+      </c>
+      <c r="AA405">
+        <v>0</v>
+      </c>
+      <c r="AB405">
+        <v>0</v>
+      </c>
+      <c r="AC405">
+        <v>0</v>
+      </c>
+      <c r="AD405">
+        <v>1</v>
+      </c>
+      <c r="AE405">
+        <v>0</v>
+      </c>
+      <c r="AF405">
+        <v>0</v>
+      </c>
+      <c r="AG405">
+        <v>1</v>
+      </c>
+      <c r="AH405">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A406">
+        <v>2026</v>
+      </c>
+      <c r="B406" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C406">
+        <v>15</v>
+      </c>
+      <c r="D406" t="s">
+        <v>76</v>
+      </c>
+      <c r="E406" t="str">
+        <f>VLOOKUP(D406,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F406" t="s">
+        <v>12</v>
+      </c>
+      <c r="G406">
+        <v>7</v>
+      </c>
+      <c r="H406">
+        <v>0</v>
+      </c>
+      <c r="I406">
+        <v>3</v>
+      </c>
+      <c r="J406" t="s">
+        <v>32</v>
+      </c>
+      <c r="K406" t="s">
+        <v>32</v>
+      </c>
+      <c r="L406">
+        <f t="shared" si="9"/>
+        <v>34</v>
+      </c>
+      <c r="M406">
+        <v>6</v>
+      </c>
+      <c r="N406">
+        <v>5</v>
+      </c>
+      <c r="O406">
+        <v>5</v>
+      </c>
+      <c r="P406">
+        <v>10</v>
+      </c>
+      <c r="Q406">
+        <v>2</v>
+      </c>
+      <c r="R406">
+        <v>12</v>
+      </c>
+      <c r="S406">
+        <v>3</v>
+      </c>
+      <c r="T406">
+        <v>0</v>
+      </c>
+      <c r="U406">
+        <v>0</v>
+      </c>
+      <c r="V406">
+        <v>2</v>
+      </c>
+      <c r="W406">
+        <v>0</v>
+      </c>
+      <c r="X406">
+        <v>0</v>
+      </c>
+      <c r="Y406">
+        <v>0</v>
+      </c>
+      <c r="Z406">
+        <v>0</v>
+      </c>
+      <c r="AA406">
+        <v>0</v>
+      </c>
+      <c r="AB406">
+        <v>0</v>
+      </c>
+      <c r="AC406">
+        <v>0</v>
+      </c>
+      <c r="AD406">
+        <v>1</v>
+      </c>
+      <c r="AE406">
+        <v>0</v>
+      </c>
+      <c r="AF406">
+        <v>1</v>
+      </c>
+      <c r="AG406">
+        <v>0</v>
+      </c>
+      <c r="AH406">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A407">
+        <v>2026</v>
+      </c>
+      <c r="B407" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C407">
+        <v>15</v>
+      </c>
+      <c r="D407" t="s">
+        <v>76</v>
+      </c>
+      <c r="E407" t="str">
+        <f>VLOOKUP(D407,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F407" t="s">
+        <v>11</v>
+      </c>
+      <c r="G407">
+        <v>10</v>
+      </c>
+      <c r="H407">
+        <v>2</v>
+      </c>
+      <c r="I407">
+        <v>2</v>
+      </c>
+      <c r="J407" t="s">
+        <v>37</v>
+      </c>
+      <c r="K407" t="s">
+        <v>32</v>
+      </c>
+      <c r="L407">
+        <f t="shared" si="9"/>
+        <v>35</v>
+      </c>
+      <c r="M407">
+        <v>5</v>
+      </c>
+      <c r="N407">
+        <v>5</v>
+      </c>
+      <c r="O407">
+        <v>6</v>
+      </c>
+      <c r="P407">
+        <v>8</v>
+      </c>
+      <c r="Q407">
+        <v>5</v>
+      </c>
+      <c r="R407">
+        <v>4</v>
+      </c>
+      <c r="S407">
+        <v>4</v>
+      </c>
+      <c r="T407">
+        <v>3</v>
+      </c>
+      <c r="U407">
+        <v>0</v>
+      </c>
+      <c r="V407">
+        <v>5</v>
+      </c>
+      <c r="W407">
+        <v>0</v>
+      </c>
+      <c r="X407">
+        <v>0</v>
+      </c>
+      <c r="Y407">
+        <v>0</v>
+      </c>
+      <c r="Z407">
+        <v>0</v>
+      </c>
+      <c r="AA407">
+        <v>0</v>
+      </c>
+      <c r="AB407">
+        <v>0</v>
+      </c>
+      <c r="AC407">
+        <v>0</v>
+      </c>
+      <c r="AD407">
+        <v>0</v>
+      </c>
+      <c r="AE407">
+        <v>0</v>
+      </c>
+      <c r="AF407">
+        <v>0</v>
+      </c>
+      <c r="AG407">
+        <v>0</v>
+      </c>
+      <c r="AH407">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AP389" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}"/>
+  <autoFilter ref="A2:AP407" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="second"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <dataValidations count="1">
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:AB8 W3:X41 Y9:Z41 W44:Z56 X58:Z116 X117:AB119 X120:Z122 X123:AB128 W58:W175 X129:Z175 W177:Z223 W225:Z299 W301:Z302 W304:Z1048576" xr:uid="{0D054DE4-3D8E-4484-9FF1-661236EA2207}">
       <formula1>0</formula1>

--- a/catan_data.xlsx
+++ b/catan_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88b1f18c208c1b3c/Documents/CatanData/catan_data/catan_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1434" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD78A930-CC68-458A-AA1A-EE0166F014F2}"/>
+  <xr:revisionPtr revIDLastSave="1435" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7C9C3D6-083B-40D8-8A88-358045BB05C0}"/>
   <bookViews>
     <workbookView xWindow="10" yWindow="10" windowWidth="22540" windowHeight="15020" xr2:uid="{83B30B11-FE95-4925-9DB4-CCB67C570BD6}"/>
   </bookViews>
@@ -656,7 +656,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AP407"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -848,7 +847,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2022</v>
       </c>
@@ -951,7 +950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2022</v>
       </c>
@@ -1054,7 +1053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2022</v>
       </c>
@@ -1157,7 +1156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2022</v>
       </c>
@@ -1260,7 +1259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2022</v>
       </c>
@@ -1363,7 +1362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2022</v>
       </c>
@@ -1466,7 +1465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2022</v>
       </c>
@@ -1569,7 +1568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2022</v>
       </c>
@@ -1672,7 +1671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2022</v>
       </c>
@@ -1775,7 +1774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2022</v>
       </c>
@@ -1878,7 +1877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2022</v>
       </c>
@@ -1981,7 +1980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2022</v>
       </c>
@@ -2084,7 +2083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2022</v>
       </c>
@@ -2187,7 +2186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2022</v>
       </c>
@@ -2290,7 +2289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2022</v>
       </c>
@@ -2393,7 +2392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2022</v>
       </c>
@@ -2496,7 +2495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2022</v>
       </c>
@@ -2599,7 +2598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2022</v>
       </c>
@@ -2702,7 +2701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2022</v>
       </c>
@@ -2805,7 +2804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2022</v>
       </c>
@@ -2908,7 +2907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2022</v>
       </c>
@@ -3320,7 +3319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2022</v>
       </c>
@@ -3426,7 +3425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2022</v>
       </c>
@@ -3532,7 +3531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2022</v>
       </c>
@@ -3956,7 +3955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>2022</v>
       </c>
@@ -4062,7 +4061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>2022</v>
       </c>
@@ -4168,7 +4167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>2022</v>
       </c>
@@ -4274,7 +4273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>2022</v>
       </c>
@@ -4380,7 +4379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>2022</v>
       </c>
@@ -4486,7 +4485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>2022</v>
       </c>
@@ -4592,7 +4591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>2022</v>
       </c>
@@ -4698,7 +4697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>2022</v>
       </c>
@@ -4804,7 +4803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>2022</v>
       </c>
@@ -4910,7 +4909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>2022</v>
       </c>
@@ -5016,7 +5015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>2022</v>
       </c>
@@ -5122,7 +5121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>2022</v>
       </c>
@@ -5228,7 +5227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>2022</v>
       </c>
@@ -5334,7 +5333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>2022</v>
       </c>
@@ -5440,7 +5439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>2022</v>
       </c>
@@ -5864,7 +5863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>2022</v>
       </c>
@@ -5970,7 +5969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>2022</v>
       </c>
@@ -6076,7 +6075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>2022</v>
       </c>
@@ -6818,7 +6817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>2022</v>
       </c>
@@ -6924,7 +6923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>2022</v>
       </c>
@@ -7030,7 +7029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>2022</v>
       </c>
@@ -7136,7 +7135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>2022</v>
       </c>
@@ -7242,7 +7241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>2022</v>
       </c>
@@ -7348,7 +7347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>2022</v>
       </c>
@@ -7454,7 +7453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>2022</v>
       </c>
@@ -7560,7 +7559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>2022</v>
       </c>
@@ -7666,7 +7665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>2022</v>
       </c>
@@ -7772,7 +7771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>2022</v>
       </c>
@@ -7878,7 +7877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>2022</v>
       </c>
@@ -7984,7 +7983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>2022</v>
       </c>
@@ -8090,7 +8089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>2022</v>
       </c>
@@ -8196,7 +8195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>2022</v>
       </c>
@@ -8302,7 +8301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>2022</v>
       </c>
@@ -8726,7 +8725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>2022</v>
       </c>
@@ -8832,7 +8831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>2022</v>
       </c>
@@ -8938,7 +8937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>2022</v>
       </c>
@@ -9044,7 +9043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>2022</v>
       </c>
@@ -9080,7 +9079,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>2022</v>
       </c>
@@ -9116,7 +9115,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="83" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>2022</v>
       </c>
@@ -9152,7 +9151,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="84" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>2022</v>
       </c>
@@ -9258,7 +9257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>2022</v>
       </c>
@@ -9364,7 +9363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>2022</v>
       </c>
@@ -9470,7 +9469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>2022</v>
       </c>
@@ -9576,7 +9575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>2022</v>
       </c>
@@ -9682,7 +9681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>2022</v>
       </c>
@@ -9788,7 +9787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>2022</v>
       </c>
@@ -9894,7 +9893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>2022</v>
       </c>
@@ -10000,7 +9999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>2022</v>
       </c>
@@ -10742,7 +10741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>2023</v>
       </c>
@@ -10848,7 +10847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>2023</v>
       </c>
@@ -10954,7 +10953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>2023</v>
       </c>
@@ -11060,7 +11059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>2023</v>
       </c>
@@ -11166,7 +11165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>2023</v>
       </c>
@@ -11272,7 +11271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>2023</v>
       </c>
@@ -12014,7 +12013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>2023</v>
       </c>
@@ -12120,7 +12119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>2023</v>
       </c>
@@ -12226,7 +12225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>2023</v>
       </c>
@@ -12332,7 +12331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>2023</v>
       </c>
@@ -12438,7 +12437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>2023</v>
       </c>
@@ -12544,7 +12543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>2023</v>
       </c>
@@ -12968,7 +12967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>2023</v>
       </c>
@@ -13001,7 +13000,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="121" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>2023</v>
       </c>
@@ -13034,7 +13033,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="122" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>2023</v>
       </c>
@@ -13067,7 +13066,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="123" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>2023</v>
       </c>
@@ -13173,7 +13172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>2023</v>
       </c>
@@ -13279,7 +13278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>2023</v>
       </c>
@@ -13703,7 +13702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>2023</v>
       </c>
@@ -13809,7 +13808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>2023</v>
       </c>
@@ -13915,7 +13914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>2023</v>
       </c>
@@ -14975,7 +14974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>2023</v>
       </c>
@@ -15081,7 +15080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>2023</v>
       </c>
@@ -15187,7 +15186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>2023</v>
       </c>
@@ -15929,7 +15928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>2023</v>
       </c>
@@ -16035,7 +16034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>2023</v>
       </c>
@@ -16141,7 +16140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>2023</v>
       </c>
@@ -16883,7 +16882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>2024</v>
       </c>
@@ -16989,7 +16988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>2024</v>
       </c>
@@ -17095,7 +17094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>2024</v>
       </c>
@@ -17837,7 +17836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>2024</v>
       </c>
@@ -17943,7 +17942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>2024</v>
       </c>
@@ -18049,7 +18048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>2024</v>
       </c>
@@ -18155,7 +18154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>2024</v>
       </c>
@@ -18261,7 +18260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>2024</v>
       </c>
@@ -18367,7 +18366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>2024</v>
       </c>
@@ -18473,7 +18472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>2024</v>
       </c>
@@ -18579,7 +18578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>2024</v>
       </c>
@@ -18685,7 +18684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>2024</v>
       </c>
@@ -18791,7 +18790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>2024</v>
       </c>
@@ -18897,7 +18896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>2024</v>
       </c>
@@ -19003,7 +19002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>2024</v>
       </c>
@@ -19427,7 +19426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>2024</v>
       </c>
@@ -19533,7 +19532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>2024</v>
       </c>
@@ -19639,7 +19638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>2024</v>
       </c>
@@ -20063,7 +20062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>2024</v>
       </c>
@@ -20169,7 +20168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>2024</v>
       </c>
@@ -20275,7 +20274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>2024</v>
       </c>
@@ -20381,7 +20380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>2024</v>
       </c>
@@ -20487,7 +20486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>2024</v>
       </c>
@@ -20593,7 +20592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>2024</v>
       </c>
@@ -21017,7 +21016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>2024</v>
       </c>
@@ -21123,7 +21122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>2024</v>
       </c>
@@ -21229,7 +21228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>2024</v>
       </c>
@@ -21653,7 +21652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>2024</v>
       </c>
@@ -21759,7 +21758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>2024</v>
       </c>
@@ -21865,7 +21864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>2024</v>
       </c>
@@ -21971,7 +21970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>2024</v>
       </c>
@@ -22077,7 +22076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>2024</v>
       </c>
@@ -22183,7 +22182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>2024</v>
       </c>
@@ -22289,7 +22288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>2024</v>
       </c>
@@ -22395,7 +22394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>2024</v>
       </c>
@@ -22501,7 +22500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>2024</v>
       </c>
@@ -22925,7 +22924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>2024</v>
       </c>
@@ -23031,7 +23030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>2024</v>
       </c>
@@ -23137,7 +23136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>2024</v>
       </c>
@@ -23879,7 +23878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>2024</v>
       </c>
@@ -23985,7 +23984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>2024</v>
       </c>
@@ -24091,7 +24090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>2024</v>
       </c>
@@ -24197,7 +24196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>2024</v>
       </c>
@@ -24303,7 +24302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>2024</v>
       </c>
@@ -24409,7 +24408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>2024</v>
       </c>
@@ -24833,7 +24832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>2024</v>
       </c>
@@ -24939,7 +24938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>2024</v>
       </c>
@@ -25045,7 +25044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>2024</v>
       </c>
@@ -25469,7 +25468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A240">
         <v>2024</v>
       </c>
@@ -25575,7 +25574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A241">
         <v>2024</v>
       </c>
@@ -25681,7 +25680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A242">
         <v>2024</v>
       </c>
@@ -25787,7 +25786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A243">
         <v>2024</v>
       </c>
@@ -25893,7 +25892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A244">
         <v>2024</v>
       </c>
@@ -25999,7 +25998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A245">
         <v>2024</v>
       </c>
@@ -26105,7 +26104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A246">
         <v>2024</v>
       </c>
@@ -26211,7 +26210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A247">
         <v>2024</v>
       </c>
@@ -26317,7 +26316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A248">
         <v>2024</v>
       </c>
@@ -26423,7 +26422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A249">
         <v>2024</v>
       </c>
@@ -26529,7 +26528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A250">
         <v>2024</v>
       </c>
@@ -26635,7 +26634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A251">
         <v>2024</v>
       </c>
@@ -26741,7 +26740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A252">
         <v>2024</v>
       </c>
@@ -26847,7 +26846,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="253" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A253">
         <v>2024</v>
       </c>
@@ -26953,7 +26952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A254">
         <v>2024</v>
       </c>
@@ -27059,7 +27058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A255">
         <v>2024</v>
       </c>
@@ -27165,7 +27164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A256">
         <v>2024</v>
       </c>
@@ -27271,7 +27270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A257">
         <v>2024</v>
       </c>
@@ -27377,7 +27376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A258">
         <v>2024</v>
       </c>
@@ -27483,7 +27482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A259">
         <v>2024</v>
       </c>
@@ -27589,7 +27588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A260">
         <v>2024</v>
       </c>
@@ -27695,7 +27694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A261">
         <v>2024</v>
       </c>
@@ -27801,7 +27800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A262">
         <v>2024</v>
       </c>
@@ -27907,7 +27906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A263">
         <v>2024</v>
       </c>
@@ -28331,7 +28330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A267">
         <v>2024</v>
       </c>
@@ -28437,7 +28436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A268">
         <v>2024</v>
       </c>
@@ -28543,7 +28542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A269">
         <v>2024</v>
       </c>
@@ -28649,7 +28648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A270">
         <v>2024</v>
       </c>
@@ -28755,7 +28754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A271">
         <v>2024</v>
       </c>
@@ -28861,7 +28860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A272">
         <v>2024</v>
       </c>
@@ -28967,7 +28966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A273">
         <v>2024</v>
       </c>
@@ -29073,7 +29072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A274">
         <v>2024</v>
       </c>
@@ -29179,7 +29178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A275">
         <v>2024</v>
       </c>
@@ -29285,7 +29284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A276">
         <v>2024</v>
       </c>
@@ -29391,7 +29390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A277">
         <v>2024</v>
       </c>
@@ -29497,7 +29496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A278">
         <v>2024</v>
       </c>
@@ -29603,7 +29602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A279">
         <v>2024</v>
       </c>
@@ -29709,7 +29708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A280">
         <v>2024</v>
       </c>
@@ -29815,7 +29814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A281">
         <v>2024</v>
       </c>
@@ -29921,7 +29920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A282">
         <v>2024</v>
       </c>
@@ -30027,7 +30026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A283">
         <v>2024</v>
       </c>
@@ -30133,7 +30132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A284">
         <v>2024</v>
       </c>
@@ -30239,7 +30238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A285">
         <v>2024</v>
       </c>
@@ -30345,7 +30344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A286">
         <v>2024</v>
       </c>
@@ -30451,7 +30450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A287">
         <v>2024</v>
       </c>
@@ -30557,7 +30556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A288">
         <v>2024</v>
       </c>
@@ -30663,7 +30662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A289">
         <v>2024</v>
       </c>
@@ -30769,7 +30768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A290">
         <v>2024</v>
       </c>
@@ -30875,7 +30874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A291">
         <v>2024</v>
       </c>
@@ -30981,7 +30980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A292">
         <v>2024</v>
       </c>
@@ -31087,7 +31086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A293">
         <v>2024</v>
       </c>
@@ -31511,7 +31510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A297">
         <v>2025</v>
       </c>
@@ -31617,7 +31616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A298">
         <v>2025</v>
       </c>
@@ -31723,7 +31722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A299">
         <v>2025</v>
       </c>
@@ -31829,7 +31828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A300">
         <v>2025</v>
       </c>
@@ -31935,7 +31934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A301">
         <v>2025</v>
       </c>
@@ -32041,7 +32040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A302">
         <v>2025</v>
       </c>
@@ -32147,7 +32146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A303">
         <v>2025</v>
       </c>
@@ -32253,7 +32252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A304">
         <v>2025</v>
       </c>
@@ -32359,7 +32358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A305">
         <v>2025</v>
       </c>
@@ -32465,7 +32464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A306">
         <v>2025</v>
       </c>
@@ -32571,7 +32570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A307">
         <v>2025</v>
       </c>
@@ -32677,7 +32676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A308">
         <v>2025</v>
       </c>
@@ -32783,7 +32782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A309">
         <v>2025</v>
       </c>
@@ -32889,7 +32888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A310">
         <v>2025</v>
       </c>
@@ -32995,7 +32994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A311">
         <v>2025</v>
       </c>
@@ -33101,7 +33100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A312">
         <v>2025</v>
       </c>
@@ -33207,7 +33206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A313">
         <v>2025</v>
       </c>
@@ -33313,7 +33312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A314">
         <v>2025</v>
       </c>
@@ -33419,7 +33418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A315">
         <v>2025</v>
       </c>
@@ -33525,7 +33524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A316">
         <v>2025</v>
       </c>
@@ -33631,7 +33630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A317">
         <v>2025</v>
       </c>
@@ -34055,7 +34054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A321">
         <v>2025</v>
       </c>
@@ -34161,7 +34160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A322">
         <v>2025</v>
       </c>
@@ -34267,7 +34266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A323">
         <v>2025</v>
       </c>
@@ -34373,7 +34372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A324">
         <v>2025</v>
       </c>
@@ -34479,7 +34478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A325">
         <v>2025</v>
       </c>
@@ -34585,7 +34584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A326">
         <v>2025</v>
       </c>
@@ -34691,7 +34690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A327">
         <v>2025</v>
       </c>
@@ -34797,7 +34796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A328">
         <v>2025</v>
       </c>
@@ -34903,7 +34902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A329">
         <v>2025</v>
       </c>
@@ -35009,7 +35008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A330">
         <v>2025</v>
       </c>
@@ -35115,7 +35114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A331">
         <v>2025</v>
       </c>
@@ -35221,7 +35220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A332">
         <v>2025</v>
       </c>
@@ -35645,7 +35644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A336">
         <v>2025</v>
       </c>
@@ -35751,7 +35750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A337">
         <v>2025</v>
       </c>
@@ -35857,7 +35856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A338">
         <v>2025</v>
       </c>
@@ -35963,7 +35962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A339">
         <v>2025</v>
       </c>
@@ -36069,7 +36068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A340">
         <v>2025</v>
       </c>
@@ -36175,7 +36174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A341">
         <v>2025</v>
       </c>
@@ -36281,7 +36280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A342">
         <v>2025</v>
       </c>
@@ -36387,7 +36386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A343">
         <v>2025</v>
       </c>
@@ -36493,7 +36492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A344">
         <v>2025</v>
       </c>
@@ -36599,7 +36598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A345">
         <v>2025</v>
       </c>
@@ -36705,7 +36704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A346">
         <v>2025</v>
       </c>
@@ -36811,7 +36810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A347">
         <v>2025</v>
       </c>
@@ -36917,7 +36916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A348">
         <v>2025</v>
       </c>
@@ -37023,7 +37022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A349">
         <v>2025</v>
       </c>
@@ -37129,7 +37128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A350">
         <v>2025</v>
       </c>
@@ -37235,7 +37234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A351">
         <v>2025</v>
       </c>
@@ -37341,7 +37340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A352">
         <v>2025</v>
       </c>
@@ -37447,7 +37446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A353">
         <v>2025</v>
       </c>
@@ -37553,7 +37552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A354">
         <v>2025</v>
       </c>
@@ -37659,7 +37658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A355">
         <v>2025</v>
       </c>
@@ -37765,7 +37764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A356">
         <v>2025</v>
       </c>
@@ -37871,7 +37870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A357">
         <v>2025</v>
       </c>
@@ -37977,7 +37976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A358">
         <v>2025</v>
       </c>
@@ -38083,7 +38082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A359">
         <v>2025</v>
       </c>
@@ -38189,7 +38188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A360">
         <v>2025</v>
       </c>
@@ -38295,7 +38294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A361">
         <v>2025</v>
       </c>
@@ -38401,7 +38400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A362">
         <v>2025</v>
       </c>
@@ -38507,7 +38506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A363">
         <v>2026</v>
       </c>
@@ -38613,7 +38612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A364">
         <v>2026</v>
       </c>
@@ -38719,7 +38718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A365">
         <v>2026</v>
       </c>
@@ -38825,7 +38824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="366" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A366">
         <v>2026</v>
       </c>
@@ -38931,7 +38930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A367">
         <v>2026</v>
       </c>
@@ -39037,7 +39036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A368">
         <v>2026</v>
       </c>
@@ -39143,7 +39142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="369" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A369">
         <v>2026</v>
       </c>
@@ -39249,7 +39248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A370">
         <v>2026</v>
       </c>
@@ -39355,7 +39354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A371">
         <v>2026</v>
       </c>
@@ -39461,7 +39460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A372">
         <v>2026</v>
       </c>
@@ -39567,7 +39566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="373" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A373">
         <v>2026</v>
       </c>
@@ -39673,7 +39672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A374">
         <v>2026</v>
       </c>
@@ -39779,7 +39778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="375" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A375">
         <v>2026</v>
       </c>
@@ -39885,7 +39884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A376">
         <v>2026</v>
       </c>
@@ -39991,7 +39990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A377">
         <v>2026</v>
       </c>
@@ -40097,7 +40096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A378">
         <v>2026</v>
       </c>
@@ -40203,7 +40202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="379" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A379">
         <v>2026</v>
       </c>
@@ -40309,7 +40308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A380">
         <v>2026</v>
       </c>
@@ -40415,7 +40414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A381">
         <v>2026</v>
       </c>
@@ -40521,7 +40520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="382" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A382">
         <v>2026</v>
       </c>
@@ -40627,7 +40626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="383" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A383">
         <v>2026</v>
       </c>
@@ -40733,7 +40732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A384">
         <v>2026</v>
       </c>
@@ -40839,7 +40838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A385">
         <v>2026</v>
       </c>
@@ -40945,7 +40944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A386">
         <v>2026</v>
       </c>
@@ -41051,7 +41050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A387">
         <v>2026</v>
       </c>
@@ -41157,7 +41156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A388">
         <v>2026</v>
       </c>
@@ -41263,7 +41262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A389">
         <v>2026</v>
       </c>
@@ -41369,7 +41368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A390">
         <v>2026</v>
       </c>
@@ -41475,7 +41474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A391">
         <v>2026</v>
       </c>
@@ -41581,7 +41580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A392">
         <v>2026</v>
       </c>
@@ -41687,7 +41686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A393">
         <v>2026</v>
       </c>
@@ -41793,7 +41792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A394">
         <v>2026</v>
       </c>
@@ -41899,7 +41898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A395">
         <v>2026</v>
       </c>
@@ -42005,7 +42004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A396">
         <v>2026</v>
       </c>
@@ -42111,7 +42110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A397">
         <v>2026</v>
       </c>
@@ -42217,7 +42216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A398">
         <v>2026</v>
       </c>
@@ -42323,7 +42322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="399" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A399">
         <v>2026</v>
       </c>
@@ -42429,7 +42428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A400">
         <v>2026</v>
       </c>
@@ -42535,7 +42534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A401">
         <v>2026</v>
       </c>
@@ -42641,7 +42640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="402" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A402">
         <v>2026</v>
       </c>
@@ -42747,7 +42746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A403">
         <v>2026</v>
       </c>
@@ -42853,7 +42852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:34" hidden="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A404">
         <v>2026</v>
       </c>
@@ -43278,13 +43277,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AP407" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}">
-    <filterColumn colId="10">
-      <filters>
-        <filter val="second"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:AP407" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}"/>
   <dataValidations count="1">
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:AB8 W3:X41 Y9:Z41 W44:Z56 X58:Z116 X117:AB119 X120:Z122 X123:AB128 W58:W175 X129:Z175 W177:Z223 W225:Z299 W301:Z302 W304:Z1048576" xr:uid="{0D054DE4-3D8E-4484-9FF1-661236EA2207}">
       <formula1>0</formula1>

--- a/catan_data.xlsx
+++ b/catan_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88b1f18c208c1b3c/Documents/CatanData/catan_data/catan_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1435" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7C9C3D6-083B-40D8-8A88-358045BB05C0}"/>
+  <xr:revisionPtr revIDLastSave="1709" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D922FFC-7413-43E9-ACFA-CABF6C2E9693}"/>
   <bookViews>
     <workbookView xWindow="10" yWindow="10" windowWidth="22540" windowHeight="15020" xr2:uid="{83B30B11-FE95-4925-9DB4-CCB67C570BD6}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$AP$407</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$AP$410</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1697" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1733" uniqueCount="79">
   <si>
     <t>season</t>
   </si>
@@ -656,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}">
-  <dimension ref="A1:AP407"/>
+  <dimension ref="A1:AP416"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -38860,7 +38860,7 @@
         <v>31</v>
       </c>
       <c r="L366">
-        <f t="shared" ref="L366:L407" si="9">SUM(O366:V366)</f>
+        <f t="shared" ref="L366:L416" si="9">SUM(O366:V366)</f>
         <v>33</v>
       </c>
       <c r="M366">
@@ -43276,8 +43276,962 @@
         <v>0</v>
       </c>
     </row>
+    <row r="408" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A408">
+        <v>2026</v>
+      </c>
+      <c r="B408" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C408">
+        <v>16</v>
+      </c>
+      <c r="D408" t="s">
+        <v>76</v>
+      </c>
+      <c r="E408" t="str">
+        <f>VLOOKUP(D408,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F408" t="s">
+        <v>13</v>
+      </c>
+      <c r="G408">
+        <v>6</v>
+      </c>
+      <c r="H408">
+        <v>1</v>
+      </c>
+      <c r="I408">
+        <v>3</v>
+      </c>
+      <c r="J408" t="s">
+        <v>36</v>
+      </c>
+      <c r="K408" t="s">
+        <v>31</v>
+      </c>
+      <c r="L408">
+        <f t="shared" si="9"/>
+        <v>28</v>
+      </c>
+      <c r="M408">
+        <v>5</v>
+      </c>
+      <c r="N408">
+        <v>4</v>
+      </c>
+      <c r="O408">
+        <v>5</v>
+      </c>
+      <c r="P408">
+        <v>0</v>
+      </c>
+      <c r="Q408">
+        <v>7</v>
+      </c>
+      <c r="R408">
+        <v>5</v>
+      </c>
+      <c r="S408">
+        <v>3</v>
+      </c>
+      <c r="T408">
+        <v>2</v>
+      </c>
+      <c r="U408">
+        <v>3</v>
+      </c>
+      <c r="V408">
+        <v>3</v>
+      </c>
+      <c r="W408">
+        <v>0</v>
+      </c>
+      <c r="X408">
+        <v>0</v>
+      </c>
+      <c r="Y408">
+        <v>0</v>
+      </c>
+      <c r="Z408">
+        <v>0</v>
+      </c>
+      <c r="AA408">
+        <v>0</v>
+      </c>
+      <c r="AB408">
+        <v>0</v>
+      </c>
+      <c r="AC408">
+        <v>0</v>
+      </c>
+      <c r="AD408">
+        <v>0</v>
+      </c>
+      <c r="AE408">
+        <v>0</v>
+      </c>
+      <c r="AF408">
+        <v>0</v>
+      </c>
+      <c r="AG408">
+        <v>0</v>
+      </c>
+      <c r="AH408">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A409">
+        <v>2026</v>
+      </c>
+      <c r="B409" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C409">
+        <v>16</v>
+      </c>
+      <c r="D409" t="s">
+        <v>76</v>
+      </c>
+      <c r="E409" t="str">
+        <f>VLOOKUP(D409,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F409" t="s">
+        <v>11</v>
+      </c>
+      <c r="G409">
+        <v>13</v>
+      </c>
+      <c r="H409">
+        <v>5</v>
+      </c>
+      <c r="I409">
+        <v>1</v>
+      </c>
+      <c r="J409" t="s">
+        <v>32</v>
+      </c>
+      <c r="K409" t="s">
+        <v>31</v>
+      </c>
+      <c r="L409">
+        <f t="shared" si="9"/>
+        <v>30</v>
+      </c>
+      <c r="M409">
+        <v>5</v>
+      </c>
+      <c r="N409">
+        <v>5</v>
+      </c>
+      <c r="O409">
+        <v>2</v>
+      </c>
+      <c r="P409">
+        <v>5</v>
+      </c>
+      <c r="Q409">
+        <v>4</v>
+      </c>
+      <c r="R409">
+        <v>4</v>
+      </c>
+      <c r="S409">
+        <v>6</v>
+      </c>
+      <c r="T409">
+        <v>2</v>
+      </c>
+      <c r="U409">
+        <v>3</v>
+      </c>
+      <c r="V409">
+        <v>4</v>
+      </c>
+      <c r="W409">
+        <v>0</v>
+      </c>
+      <c r="X409">
+        <v>0</v>
+      </c>
+      <c r="Y409">
+        <v>0</v>
+      </c>
+      <c r="Z409">
+        <v>0</v>
+      </c>
+      <c r="AA409">
+        <v>0</v>
+      </c>
+      <c r="AB409">
+        <v>0</v>
+      </c>
+      <c r="AC409">
+        <v>0</v>
+      </c>
+      <c r="AD409">
+        <v>1</v>
+      </c>
+      <c r="AE409">
+        <v>0</v>
+      </c>
+      <c r="AF409">
+        <v>0</v>
+      </c>
+      <c r="AG409">
+        <v>0</v>
+      </c>
+      <c r="AH409">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="410" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A410">
+        <v>2026</v>
+      </c>
+      <c r="B410" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C410">
+        <v>16</v>
+      </c>
+      <c r="D410" t="s">
+        <v>76</v>
+      </c>
+      <c r="E410" t="str">
+        <f>VLOOKUP(D410,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F410" t="s">
+        <v>12</v>
+      </c>
+      <c r="G410">
+        <v>8</v>
+      </c>
+      <c r="H410">
+        <v>2</v>
+      </c>
+      <c r="I410">
+        <v>2</v>
+      </c>
+      <c r="J410" t="s">
+        <v>37</v>
+      </c>
+      <c r="K410" t="s">
+        <v>31</v>
+      </c>
+      <c r="L410">
+        <f t="shared" si="9"/>
+        <v>37</v>
+      </c>
+      <c r="M410">
+        <v>4</v>
+      </c>
+      <c r="N410">
+        <v>4</v>
+      </c>
+      <c r="O410">
+        <v>0</v>
+      </c>
+      <c r="P410">
+        <v>4</v>
+      </c>
+      <c r="Q410">
+        <v>8</v>
+      </c>
+      <c r="R410">
+        <v>6</v>
+      </c>
+      <c r="S410">
+        <v>10</v>
+      </c>
+      <c r="T410">
+        <v>0</v>
+      </c>
+      <c r="U410">
+        <v>5</v>
+      </c>
+      <c r="V410">
+        <v>4</v>
+      </c>
+      <c r="W410">
+        <v>0</v>
+      </c>
+      <c r="X410">
+        <v>0</v>
+      </c>
+      <c r="Y410">
+        <v>0</v>
+      </c>
+      <c r="Z410">
+        <v>0</v>
+      </c>
+      <c r="AA410">
+        <v>0</v>
+      </c>
+      <c r="AB410">
+        <v>0</v>
+      </c>
+      <c r="AC410">
+        <v>1</v>
+      </c>
+      <c r="AD410">
+        <v>0</v>
+      </c>
+      <c r="AE410">
+        <v>0</v>
+      </c>
+      <c r="AF410">
+        <v>0</v>
+      </c>
+      <c r="AG410">
+        <v>1</v>
+      </c>
+      <c r="AH410">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A411">
+        <v>2026</v>
+      </c>
+      <c r="B411" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C411">
+        <v>17</v>
+      </c>
+      <c r="D411" t="s">
+        <v>76</v>
+      </c>
+      <c r="E411" t="str">
+        <f>VLOOKUP(D411,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F411" t="s">
+        <v>11</v>
+      </c>
+      <c r="G411">
+        <v>13</v>
+      </c>
+      <c r="H411">
+        <v>7</v>
+      </c>
+      <c r="I411">
+        <v>1</v>
+      </c>
+      <c r="J411" t="s">
+        <v>36</v>
+      </c>
+      <c r="K411" t="s">
+        <v>31</v>
+      </c>
+      <c r="L411">
+        <f t="shared" si="9"/>
+        <v>34</v>
+      </c>
+      <c r="M411">
+        <v>5</v>
+      </c>
+      <c r="N411">
+        <v>4</v>
+      </c>
+      <c r="O411">
+        <v>0</v>
+      </c>
+      <c r="P411">
+        <v>8</v>
+      </c>
+      <c r="Q411">
+        <v>7</v>
+      </c>
+      <c r="R411">
+        <v>4</v>
+      </c>
+      <c r="S411">
+        <v>4</v>
+      </c>
+      <c r="T411">
+        <v>0</v>
+      </c>
+      <c r="U411">
+        <v>4</v>
+      </c>
+      <c r="V411">
+        <v>7</v>
+      </c>
+      <c r="W411">
+        <v>0</v>
+      </c>
+      <c r="X411">
+        <v>0</v>
+      </c>
+      <c r="Y411">
+        <v>0</v>
+      </c>
+      <c r="Z411">
+        <v>0</v>
+      </c>
+      <c r="AA411">
+        <v>0</v>
+      </c>
+      <c r="AB411">
+        <v>0</v>
+      </c>
+      <c r="AC411">
+        <v>1</v>
+      </c>
+      <c r="AD411">
+        <v>0</v>
+      </c>
+      <c r="AE411">
+        <v>0</v>
+      </c>
+      <c r="AF411">
+        <v>0</v>
+      </c>
+      <c r="AG411">
+        <v>0</v>
+      </c>
+      <c r="AH411">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A412">
+        <v>2026</v>
+      </c>
+      <c r="B412" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C412">
+        <v>17</v>
+      </c>
+      <c r="D412" t="s">
+        <v>76</v>
+      </c>
+      <c r="E412" t="str">
+        <f>VLOOKUP(D412,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F412" t="s">
+        <v>13</v>
+      </c>
+      <c r="G412">
+        <v>9</v>
+      </c>
+      <c r="H412">
+        <v>3</v>
+      </c>
+      <c r="I412">
+        <v>2</v>
+      </c>
+      <c r="J412" t="s">
+        <v>32</v>
+      </c>
+      <c r="K412" t="s">
+        <v>31</v>
+      </c>
+      <c r="L412">
+        <f t="shared" si="9"/>
+        <v>31</v>
+      </c>
+      <c r="M412">
+        <v>6</v>
+      </c>
+      <c r="N412">
+        <v>5</v>
+      </c>
+      <c r="O412">
+        <v>3</v>
+      </c>
+      <c r="P412">
+        <v>4</v>
+      </c>
+      <c r="Q412">
+        <v>5</v>
+      </c>
+      <c r="R412">
+        <v>4</v>
+      </c>
+      <c r="S412">
+        <v>7</v>
+      </c>
+      <c r="T412">
+        <v>0</v>
+      </c>
+      <c r="U412">
+        <v>3</v>
+      </c>
+      <c r="V412">
+        <v>5</v>
+      </c>
+      <c r="W412">
+        <v>0</v>
+      </c>
+      <c r="X412">
+        <v>0</v>
+      </c>
+      <c r="Y412">
+        <v>0</v>
+      </c>
+      <c r="Z412">
+        <v>0</v>
+      </c>
+      <c r="AA412">
+        <v>0</v>
+      </c>
+      <c r="AB412">
+        <v>0</v>
+      </c>
+      <c r="AC412">
+        <v>0</v>
+      </c>
+      <c r="AD412">
+        <v>0</v>
+      </c>
+      <c r="AE412">
+        <v>0</v>
+      </c>
+      <c r="AF412">
+        <v>0</v>
+      </c>
+      <c r="AG412">
+        <v>0</v>
+      </c>
+      <c r="AH412">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="413" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A413">
+        <v>2026</v>
+      </c>
+      <c r="B413" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C413">
+        <v>17</v>
+      </c>
+      <c r="D413" t="s">
+        <v>76</v>
+      </c>
+      <c r="E413" t="str">
+        <f>VLOOKUP(D413,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F413" t="s">
+        <v>12</v>
+      </c>
+      <c r="G413">
+        <v>8</v>
+      </c>
+      <c r="H413">
+        <v>0</v>
+      </c>
+      <c r="I413">
+        <v>3</v>
+      </c>
+      <c r="J413" t="s">
+        <v>37</v>
+      </c>
+      <c r="K413" t="s">
+        <v>31</v>
+      </c>
+      <c r="L413">
+        <f t="shared" si="9"/>
+        <v>33</v>
+      </c>
+      <c r="M413">
+        <v>6</v>
+      </c>
+      <c r="N413">
+        <v>4</v>
+      </c>
+      <c r="O413">
+        <v>5</v>
+      </c>
+      <c r="P413">
+        <v>0</v>
+      </c>
+      <c r="Q413">
+        <v>9</v>
+      </c>
+      <c r="R413">
+        <v>5</v>
+      </c>
+      <c r="S413">
+        <v>3</v>
+      </c>
+      <c r="T413">
+        <v>3</v>
+      </c>
+      <c r="U413">
+        <v>3</v>
+      </c>
+      <c r="V413">
+        <v>5</v>
+      </c>
+      <c r="W413">
+        <v>0</v>
+      </c>
+      <c r="X413">
+        <v>0</v>
+      </c>
+      <c r="Y413">
+        <v>0</v>
+      </c>
+      <c r="Z413">
+        <v>0</v>
+      </c>
+      <c r="AA413">
+        <v>0</v>
+      </c>
+      <c r="AB413">
+        <v>0</v>
+      </c>
+      <c r="AC413">
+        <v>0</v>
+      </c>
+      <c r="AD413">
+        <v>0</v>
+      </c>
+      <c r="AE413">
+        <v>0</v>
+      </c>
+      <c r="AF413">
+        <v>1</v>
+      </c>
+      <c r="AG413">
+        <v>0</v>
+      </c>
+      <c r="AH413">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A414">
+        <v>2026</v>
+      </c>
+      <c r="B414" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C414">
+        <v>18</v>
+      </c>
+      <c r="D414" t="s">
+        <v>76</v>
+      </c>
+      <c r="E414" t="str">
+        <f>VLOOKUP(D414,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F414" t="s">
+        <v>12</v>
+      </c>
+      <c r="G414">
+        <v>9</v>
+      </c>
+      <c r="H414">
+        <v>1</v>
+      </c>
+      <c r="I414">
+        <v>2</v>
+      </c>
+      <c r="J414" t="s">
+        <v>36</v>
+      </c>
+      <c r="K414" t="s">
+        <v>32</v>
+      </c>
+      <c r="L414">
+        <f t="shared" si="9"/>
+        <v>35</v>
+      </c>
+      <c r="M414">
+        <v>6</v>
+      </c>
+      <c r="N414">
+        <v>4</v>
+      </c>
+      <c r="O414">
+        <v>3</v>
+      </c>
+      <c r="P414">
+        <v>8</v>
+      </c>
+      <c r="Q414">
+        <v>0</v>
+      </c>
+      <c r="R414">
+        <v>8</v>
+      </c>
+      <c r="S414">
+        <v>9</v>
+      </c>
+      <c r="T414">
+        <v>3</v>
+      </c>
+      <c r="U414">
+        <v>4</v>
+      </c>
+      <c r="V414">
+        <v>0</v>
+      </c>
+      <c r="W414">
+        <v>0</v>
+      </c>
+      <c r="X414">
+        <v>0</v>
+      </c>
+      <c r="Y414">
+        <v>0</v>
+      </c>
+      <c r="Z414">
+        <v>0</v>
+      </c>
+      <c r="AA414">
+        <v>0</v>
+      </c>
+      <c r="AB414">
+        <v>0</v>
+      </c>
+      <c r="AC414">
+        <v>0</v>
+      </c>
+      <c r="AD414">
+        <v>0</v>
+      </c>
+      <c r="AE414">
+        <v>0</v>
+      </c>
+      <c r="AF414">
+        <v>0</v>
+      </c>
+      <c r="AG414">
+        <v>0</v>
+      </c>
+      <c r="AH414">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A415">
+        <v>2026</v>
+      </c>
+      <c r="B415" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C415">
+        <v>18</v>
+      </c>
+      <c r="D415" t="s">
+        <v>76</v>
+      </c>
+      <c r="E415" t="str">
+        <f>VLOOKUP(D415,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F415" t="s">
+        <v>11</v>
+      </c>
+      <c r="G415">
+        <v>13</v>
+      </c>
+      <c r="H415">
+        <v>6</v>
+      </c>
+      <c r="I415">
+        <v>1</v>
+      </c>
+      <c r="J415" t="s">
+        <v>32</v>
+      </c>
+      <c r="K415" t="s">
+        <v>32</v>
+      </c>
+      <c r="L415">
+        <f t="shared" si="9"/>
+        <v>30</v>
+      </c>
+      <c r="M415">
+        <v>5</v>
+      </c>
+      <c r="N415">
+        <v>4</v>
+      </c>
+      <c r="O415">
+        <v>3</v>
+      </c>
+      <c r="P415">
+        <v>5</v>
+      </c>
+      <c r="Q415">
+        <v>6</v>
+      </c>
+      <c r="R415">
+        <v>10</v>
+      </c>
+      <c r="S415">
+        <v>0</v>
+      </c>
+      <c r="T415">
+        <v>0</v>
+      </c>
+      <c r="U415">
+        <v>0</v>
+      </c>
+      <c r="V415">
+        <v>6</v>
+      </c>
+      <c r="W415">
+        <v>0</v>
+      </c>
+      <c r="X415">
+        <v>0</v>
+      </c>
+      <c r="Y415">
+        <v>0</v>
+      </c>
+      <c r="Z415">
+        <v>0</v>
+      </c>
+      <c r="AA415">
+        <v>0</v>
+      </c>
+      <c r="AB415">
+        <v>0</v>
+      </c>
+      <c r="AC415">
+        <v>0</v>
+      </c>
+      <c r="AD415">
+        <v>1</v>
+      </c>
+      <c r="AE415">
+        <v>0</v>
+      </c>
+      <c r="AF415">
+        <v>0</v>
+      </c>
+      <c r="AG415">
+        <v>0</v>
+      </c>
+      <c r="AH415">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A416">
+        <v>2026</v>
+      </c>
+      <c r="B416" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C416">
+        <v>18</v>
+      </c>
+      <c r="D416" t="s">
+        <v>76</v>
+      </c>
+      <c r="E416" t="str">
+        <f>VLOOKUP(D416,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F416" t="s">
+        <v>13</v>
+      </c>
+      <c r="G416">
+        <v>8</v>
+      </c>
+      <c r="H416">
+        <v>2</v>
+      </c>
+      <c r="I416">
+        <v>3</v>
+      </c>
+      <c r="J416" t="s">
+        <v>37</v>
+      </c>
+      <c r="K416" t="s">
+        <v>32</v>
+      </c>
+      <c r="L416">
+        <f t="shared" si="9"/>
+        <v>33</v>
+      </c>
+      <c r="M416">
+        <v>4</v>
+      </c>
+      <c r="N416">
+        <v>4</v>
+      </c>
+      <c r="O416">
+        <v>3</v>
+      </c>
+      <c r="P416">
+        <v>0</v>
+      </c>
+      <c r="Q416">
+        <v>5</v>
+      </c>
+      <c r="R416">
+        <v>4</v>
+      </c>
+      <c r="S416">
+        <v>9</v>
+      </c>
+      <c r="T416">
+        <v>3</v>
+      </c>
+      <c r="U416">
+        <v>4</v>
+      </c>
+      <c r="V416">
+        <v>5</v>
+      </c>
+      <c r="W416">
+        <v>0</v>
+      </c>
+      <c r="X416">
+        <v>0</v>
+      </c>
+      <c r="Y416">
+        <v>0</v>
+      </c>
+      <c r="Z416">
+        <v>0</v>
+      </c>
+      <c r="AA416">
+        <v>0</v>
+      </c>
+      <c r="AB416">
+        <v>0</v>
+      </c>
+      <c r="AC416">
+        <v>0</v>
+      </c>
+      <c r="AD416">
+        <v>0</v>
+      </c>
+      <c r="AE416">
+        <v>0</v>
+      </c>
+      <c r="AF416">
+        <v>0</v>
+      </c>
+      <c r="AG416">
+        <v>0</v>
+      </c>
+      <c r="AH416">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AP407" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}"/>
+  <autoFilter ref="A2:AP410" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}"/>
   <dataValidations count="1">
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:AB8 W3:X41 Y9:Z41 W44:Z56 X58:Z116 X117:AB119 X120:Z122 X123:AB128 W58:W175 X129:Z175 W177:Z223 W225:Z299 W301:Z302 W304:Z1048576" xr:uid="{0D054DE4-3D8E-4484-9FF1-661236EA2207}">
       <formula1>0</formula1>

--- a/catan_data.xlsx
+++ b/catan_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88b1f18c208c1b3c/Documents/CatanData/catan_data/catan_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1709" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D922FFC-7413-43E9-ACFA-CABF6C2E9693}"/>
+  <xr:revisionPtr revIDLastSave="1801" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F177FCD-E8DF-45CB-9192-0D617592940D}"/>
   <bookViews>
     <workbookView xWindow="10" yWindow="10" windowWidth="22540" windowHeight="15020" xr2:uid="{83B30B11-FE95-4925-9DB4-CCB67C570BD6}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1733" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1745" uniqueCount="79">
   <si>
     <t>season</t>
   </si>
@@ -656,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}">
-  <dimension ref="A1:AP416"/>
+  <dimension ref="A1:AP419"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -38860,7 +38860,7 @@
         <v>31</v>
       </c>
       <c r="L366">
-        <f t="shared" ref="L366:L416" si="9">SUM(O366:V366)</f>
+        <f t="shared" ref="L366:L419" si="9">SUM(O366:V366)</f>
         <v>33</v>
       </c>
       <c r="M366">
@@ -44228,6 +44228,324 @@
       </c>
       <c r="AH416">
         <v>1</v>
+      </c>
+    </row>
+    <row r="417" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A417">
+        <v>2026</v>
+      </c>
+      <c r="B417" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C417">
+        <v>19</v>
+      </c>
+      <c r="D417" t="s">
+        <v>76</v>
+      </c>
+      <c r="E417" t="str">
+        <f>VLOOKUP(D417,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F417" t="s">
+        <v>11</v>
+      </c>
+      <c r="G417">
+        <v>10</v>
+      </c>
+      <c r="H417">
+        <v>2</v>
+      </c>
+      <c r="I417">
+        <v>3</v>
+      </c>
+      <c r="J417" t="s">
+        <v>36</v>
+      </c>
+      <c r="K417" t="s">
+        <v>31</v>
+      </c>
+      <c r="L417">
+        <f t="shared" si="9"/>
+        <v>28</v>
+      </c>
+      <c r="M417">
+        <v>5</v>
+      </c>
+      <c r="N417">
+        <v>5</v>
+      </c>
+      <c r="O417">
+        <v>5</v>
+      </c>
+      <c r="P417">
+        <v>4</v>
+      </c>
+      <c r="Q417">
+        <v>3</v>
+      </c>
+      <c r="R417">
+        <v>5</v>
+      </c>
+      <c r="S417">
+        <v>3</v>
+      </c>
+      <c r="T417">
+        <v>5</v>
+      </c>
+      <c r="U417">
+        <v>0</v>
+      </c>
+      <c r="V417">
+        <v>3</v>
+      </c>
+      <c r="W417">
+        <v>0</v>
+      </c>
+      <c r="X417">
+        <v>0</v>
+      </c>
+      <c r="Y417">
+        <v>0</v>
+      </c>
+      <c r="Z417">
+        <v>1</v>
+      </c>
+      <c r="AA417">
+        <v>0</v>
+      </c>
+      <c r="AB417">
+        <v>0</v>
+      </c>
+      <c r="AC417">
+        <v>0</v>
+      </c>
+      <c r="AD417">
+        <v>0</v>
+      </c>
+      <c r="AE417">
+        <v>0</v>
+      </c>
+      <c r="AF417">
+        <v>0</v>
+      </c>
+      <c r="AG417">
+        <v>0</v>
+      </c>
+      <c r="AH417">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A418">
+        <v>2026</v>
+      </c>
+      <c r="B418" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C418">
+        <v>19</v>
+      </c>
+      <c r="D418" t="s">
+        <v>76</v>
+      </c>
+      <c r="E418" t="str">
+        <f>VLOOKUP(D418,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F418" t="s">
+        <v>13</v>
+      </c>
+      <c r="G418">
+        <v>13</v>
+      </c>
+      <c r="H418">
+        <v>7</v>
+      </c>
+      <c r="I418">
+        <v>1</v>
+      </c>
+      <c r="J418" t="s">
+        <v>32</v>
+      </c>
+      <c r="K418" t="s">
+        <v>31</v>
+      </c>
+      <c r="L418">
+        <f t="shared" si="9"/>
+        <v>30</v>
+      </c>
+      <c r="M418">
+        <v>6</v>
+      </c>
+      <c r="N418">
+        <v>5</v>
+      </c>
+      <c r="O418">
+        <v>4</v>
+      </c>
+      <c r="P418">
+        <v>3</v>
+      </c>
+      <c r="Q418">
+        <v>5</v>
+      </c>
+      <c r="R418">
+        <v>10</v>
+      </c>
+      <c r="S418">
+        <v>4</v>
+      </c>
+      <c r="T418">
+        <v>0</v>
+      </c>
+      <c r="U418">
+        <v>4</v>
+      </c>
+      <c r="V418">
+        <v>0</v>
+      </c>
+      <c r="W418">
+        <v>0</v>
+      </c>
+      <c r="X418">
+        <v>0</v>
+      </c>
+      <c r="Y418">
+        <v>0</v>
+      </c>
+      <c r="Z418">
+        <v>0</v>
+      </c>
+      <c r="AA418">
+        <v>0</v>
+      </c>
+      <c r="AB418">
+        <v>0</v>
+      </c>
+      <c r="AC418">
+        <v>0</v>
+      </c>
+      <c r="AD418">
+        <v>0</v>
+      </c>
+      <c r="AE418">
+        <v>0</v>
+      </c>
+      <c r="AF418">
+        <v>0</v>
+      </c>
+      <c r="AG418">
+        <v>0</v>
+      </c>
+      <c r="AH418">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="419" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A419">
+        <v>2026</v>
+      </c>
+      <c r="B419" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C419">
+        <v>19</v>
+      </c>
+      <c r="D419" t="s">
+        <v>76</v>
+      </c>
+      <c r="E419" t="str">
+        <f>VLOOKUP(D419,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F419" t="s">
+        <v>12</v>
+      </c>
+      <c r="G419">
+        <v>11</v>
+      </c>
+      <c r="H419">
+        <v>2</v>
+      </c>
+      <c r="I419">
+        <v>2</v>
+      </c>
+      <c r="J419" t="s">
+        <v>37</v>
+      </c>
+      <c r="K419" t="s">
+        <v>31</v>
+      </c>
+      <c r="L419">
+        <f t="shared" si="9"/>
+        <v>36</v>
+      </c>
+      <c r="M419">
+        <v>6</v>
+      </c>
+      <c r="N419">
+        <v>4</v>
+      </c>
+      <c r="O419">
+        <v>9</v>
+      </c>
+      <c r="P419">
+        <v>3</v>
+      </c>
+      <c r="Q419">
+        <v>5</v>
+      </c>
+      <c r="R419">
+        <v>10</v>
+      </c>
+      <c r="S419">
+        <v>0</v>
+      </c>
+      <c r="T419">
+        <v>9</v>
+      </c>
+      <c r="U419">
+        <v>0</v>
+      </c>
+      <c r="V419">
+        <v>0</v>
+      </c>
+      <c r="W419">
+        <v>0</v>
+      </c>
+      <c r="X419">
+        <v>0</v>
+      </c>
+      <c r="Y419">
+        <v>0</v>
+      </c>
+      <c r="Z419">
+        <v>0</v>
+      </c>
+      <c r="AA419">
+        <v>0</v>
+      </c>
+      <c r="AB419">
+        <v>0</v>
+      </c>
+      <c r="AC419">
+        <v>0</v>
+      </c>
+      <c r="AD419">
+        <v>0</v>
+      </c>
+      <c r="AE419">
+        <v>0</v>
+      </c>
+      <c r="AF419">
+        <v>0</v>
+      </c>
+      <c r="AG419">
+        <v>0</v>
+      </c>
+      <c r="AH419">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/catan_data.xlsx
+++ b/catan_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88b1f18c208c1b3c/Documents/CatanData/catan_data/catan_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1801" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F177FCD-E8DF-45CB-9192-0D617592940D}"/>
+  <xr:revisionPtr revIDLastSave="1891" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE4F6B44-C5F6-4987-A71C-93ED65F95C03}"/>
   <bookViews>
     <workbookView xWindow="10" yWindow="10" windowWidth="22540" windowHeight="15020" xr2:uid="{83B30B11-FE95-4925-9DB4-CCB67C570BD6}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1745" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="79">
   <si>
     <t>season</t>
   </si>
@@ -656,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}">
-  <dimension ref="A1:AP419"/>
+  <dimension ref="A1:AP422"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -38860,7 +38860,7 @@
         <v>31</v>
       </c>
       <c r="L366">
-        <f t="shared" ref="L366:L419" si="9">SUM(O366:V366)</f>
+        <f t="shared" ref="L366:L422" si="9">SUM(O366:V366)</f>
         <v>33</v>
       </c>
       <c r="M366">
@@ -44545,6 +44545,324 @@
         <v>0</v>
       </c>
       <c r="AH419">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A420">
+        <v>2026</v>
+      </c>
+      <c r="B420" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C420">
+        <v>20</v>
+      </c>
+      <c r="D420" t="s">
+        <v>76</v>
+      </c>
+      <c r="E420" t="str">
+        <f>VLOOKUP(D420,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F420" t="s">
+        <v>11</v>
+      </c>
+      <c r="G420">
+        <v>13</v>
+      </c>
+      <c r="H420">
+        <v>6</v>
+      </c>
+      <c r="I420">
+        <v>1</v>
+      </c>
+      <c r="J420" t="s">
+        <v>36</v>
+      </c>
+      <c r="K420" t="s">
+        <v>31</v>
+      </c>
+      <c r="L420">
+        <f t="shared" si="9"/>
+        <v>31</v>
+      </c>
+      <c r="M420">
+        <v>5</v>
+      </c>
+      <c r="N420">
+        <v>4</v>
+      </c>
+      <c r="O420">
+        <v>4</v>
+      </c>
+      <c r="P420">
+        <v>0</v>
+      </c>
+      <c r="Q420">
+        <v>8</v>
+      </c>
+      <c r="R420">
+        <v>9</v>
+      </c>
+      <c r="S420">
+        <v>3</v>
+      </c>
+      <c r="T420">
+        <v>0</v>
+      </c>
+      <c r="U420">
+        <v>3</v>
+      </c>
+      <c r="V420">
+        <v>4</v>
+      </c>
+      <c r="W420">
+        <v>0</v>
+      </c>
+      <c r="X420">
+        <v>0</v>
+      </c>
+      <c r="Y420">
+        <v>0</v>
+      </c>
+      <c r="Z420">
+        <v>0</v>
+      </c>
+      <c r="AA420">
+        <v>0</v>
+      </c>
+      <c r="AB420">
+        <v>0</v>
+      </c>
+      <c r="AC420">
+        <v>0</v>
+      </c>
+      <c r="AD420">
+        <v>0</v>
+      </c>
+      <c r="AE420">
+        <v>0</v>
+      </c>
+      <c r="AF420">
+        <v>1</v>
+      </c>
+      <c r="AG420">
+        <v>0</v>
+      </c>
+      <c r="AH420">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A421">
+        <v>2026</v>
+      </c>
+      <c r="B421" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C421">
+        <v>20</v>
+      </c>
+      <c r="D421" t="s">
+        <v>76</v>
+      </c>
+      <c r="E421" t="str">
+        <f>VLOOKUP(D421,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F421" t="s">
+        <v>13</v>
+      </c>
+      <c r="G421">
+        <v>4</v>
+      </c>
+      <c r="H421">
+        <v>0</v>
+      </c>
+      <c r="I421">
+        <v>3</v>
+      </c>
+      <c r="J421" t="s">
+        <v>32</v>
+      </c>
+      <c r="K421" t="s">
+        <v>31</v>
+      </c>
+      <c r="L421">
+        <f>SUM(P421:V421)</f>
+        <v>25</v>
+      </c>
+      <c r="M421">
+        <v>4</v>
+      </c>
+      <c r="N421">
+        <v>4</v>
+      </c>
+      <c r="O421">
+        <v>3</v>
+      </c>
+      <c r="P421">
+        <v>15</v>
+      </c>
+      <c r="Q421">
+        <v>0</v>
+      </c>
+      <c r="R421">
+        <v>4</v>
+      </c>
+      <c r="S421">
+        <v>3</v>
+      </c>
+      <c r="T421">
+        <v>3</v>
+      </c>
+      <c r="U421">
+        <v>0</v>
+      </c>
+      <c r="V421">
+        <v>0</v>
+      </c>
+      <c r="W421">
+        <v>0</v>
+      </c>
+      <c r="X421">
+        <v>1</v>
+      </c>
+      <c r="Y421">
+        <v>0</v>
+      </c>
+      <c r="Z421">
+        <v>0</v>
+      </c>
+      <c r="AA421">
+        <v>0</v>
+      </c>
+      <c r="AB421">
+        <v>0</v>
+      </c>
+      <c r="AC421">
+        <v>0</v>
+      </c>
+      <c r="AD421">
+        <v>0</v>
+      </c>
+      <c r="AE421">
+        <v>0</v>
+      </c>
+      <c r="AF421">
+        <v>0</v>
+      </c>
+      <c r="AG421">
+        <v>0</v>
+      </c>
+      <c r="AH421">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A422">
+        <v>2026</v>
+      </c>
+      <c r="B422" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C422">
+        <v>20</v>
+      </c>
+      <c r="D422" t="s">
+        <v>76</v>
+      </c>
+      <c r="E422" t="str">
+        <f>VLOOKUP(D422,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F422" t="s">
+        <v>12</v>
+      </c>
+      <c r="G422">
+        <v>8</v>
+      </c>
+      <c r="H422">
+        <v>2</v>
+      </c>
+      <c r="I422">
+        <v>2</v>
+      </c>
+      <c r="J422" t="s">
+        <v>37</v>
+      </c>
+      <c r="K422" t="s">
+        <v>31</v>
+      </c>
+      <c r="L422">
+        <f t="shared" si="9"/>
+        <v>35</v>
+      </c>
+      <c r="M422">
+        <v>6</v>
+      </c>
+      <c r="N422">
+        <v>4</v>
+      </c>
+      <c r="O422">
+        <v>5</v>
+      </c>
+      <c r="P422">
+        <v>5</v>
+      </c>
+      <c r="Q422">
+        <v>11</v>
+      </c>
+      <c r="R422">
+        <v>0</v>
+      </c>
+      <c r="S422">
+        <v>2</v>
+      </c>
+      <c r="T422">
+        <v>5</v>
+      </c>
+      <c r="U422">
+        <v>0</v>
+      </c>
+      <c r="V422">
+        <v>7</v>
+      </c>
+      <c r="W422">
+        <v>0</v>
+      </c>
+      <c r="X422">
+        <v>0</v>
+      </c>
+      <c r="Y422">
+        <v>0</v>
+      </c>
+      <c r="Z422">
+        <v>0</v>
+      </c>
+      <c r="AA422">
+        <v>0</v>
+      </c>
+      <c r="AB422">
+        <v>0</v>
+      </c>
+      <c r="AC422">
+        <v>0</v>
+      </c>
+      <c r="AD422">
+        <v>0</v>
+      </c>
+      <c r="AE422">
+        <v>1</v>
+      </c>
+      <c r="AF422">
+        <v>0</v>
+      </c>
+      <c r="AG422">
+        <v>0</v>
+      </c>
+      <c r="AH422">
         <v>0</v>
       </c>
     </row>

--- a/catan_data.xlsx
+++ b/catan_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88b1f18c208c1b3c/Documents/CatanData/catan_data/catan_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1891" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE4F6B44-C5F6-4987-A71C-93ED65F95C03}"/>
+  <xr:revisionPtr revIDLastSave="1983" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FBB7069-6753-481C-A382-73F6147AB879}"/>
   <bookViews>
     <workbookView xWindow="10" yWindow="10" windowWidth="22540" windowHeight="15020" xr2:uid="{83B30B11-FE95-4925-9DB4-CCB67C570BD6}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="79">
   <si>
     <t>season</t>
   </si>
@@ -656,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}">
-  <dimension ref="A1:AP422"/>
+  <dimension ref="A1:AP425"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -38860,7 +38860,7 @@
         <v>31</v>
       </c>
       <c r="L366">
-        <f t="shared" ref="L366:L422" si="9">SUM(O366:V366)</f>
+        <f t="shared" ref="L366:L425" si="9">SUM(O366:V366)</f>
         <v>33</v>
       </c>
       <c r="M366">
@@ -44863,6 +44863,324 @@
         <v>0</v>
       </c>
       <c r="AH422">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A423">
+        <v>2026</v>
+      </c>
+      <c r="B423" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C423">
+        <v>21</v>
+      </c>
+      <c r="D423" t="s">
+        <v>76</v>
+      </c>
+      <c r="E423" t="str">
+        <f>VLOOKUP(D423,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F423" t="s">
+        <v>11</v>
+      </c>
+      <c r="G423">
+        <v>13</v>
+      </c>
+      <c r="H423">
+        <v>5</v>
+      </c>
+      <c r="I423">
+        <v>1</v>
+      </c>
+      <c r="J423" t="s">
+        <v>36</v>
+      </c>
+      <c r="K423" t="s">
+        <v>31</v>
+      </c>
+      <c r="L423">
+        <f t="shared" si="9"/>
+        <v>28</v>
+      </c>
+      <c r="M423">
+        <v>5</v>
+      </c>
+      <c r="N423">
+        <v>3</v>
+      </c>
+      <c r="O423">
+        <v>0</v>
+      </c>
+      <c r="P423">
+        <v>3</v>
+      </c>
+      <c r="Q423">
+        <v>0</v>
+      </c>
+      <c r="R423">
+        <v>4</v>
+      </c>
+      <c r="S423">
+        <v>13</v>
+      </c>
+      <c r="T423">
+        <v>0</v>
+      </c>
+      <c r="U423">
+        <v>8</v>
+      </c>
+      <c r="V423">
+        <v>0</v>
+      </c>
+      <c r="W423">
+        <v>0</v>
+      </c>
+      <c r="X423">
+        <v>0</v>
+      </c>
+      <c r="Y423">
+        <v>0</v>
+      </c>
+      <c r="Z423">
+        <v>1</v>
+      </c>
+      <c r="AA423">
+        <v>0</v>
+      </c>
+      <c r="AB423">
+        <v>0</v>
+      </c>
+      <c r="AC423">
+        <v>1</v>
+      </c>
+      <c r="AD423">
+        <v>0</v>
+      </c>
+      <c r="AE423">
+        <v>0</v>
+      </c>
+      <c r="AF423">
+        <v>0</v>
+      </c>
+      <c r="AG423">
+        <v>0</v>
+      </c>
+      <c r="AH423">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A424">
+        <v>2026</v>
+      </c>
+      <c r="B424" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C424">
+        <v>21</v>
+      </c>
+      <c r="D424" t="s">
+        <v>76</v>
+      </c>
+      <c r="E424" t="str">
+        <f>VLOOKUP(D424,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F424" t="s">
+        <v>13</v>
+      </c>
+      <c r="G424">
+        <v>9</v>
+      </c>
+      <c r="H424">
+        <v>2</v>
+      </c>
+      <c r="I424">
+        <v>2</v>
+      </c>
+      <c r="J424" t="s">
+        <v>32</v>
+      </c>
+      <c r="K424" t="s">
+        <v>31</v>
+      </c>
+      <c r="L424">
+        <f t="shared" si="9"/>
+        <v>34</v>
+      </c>
+      <c r="M424">
+        <v>5</v>
+      </c>
+      <c r="N424">
+        <v>4</v>
+      </c>
+      <c r="O424">
+        <v>10</v>
+      </c>
+      <c r="P424">
+        <v>4</v>
+      </c>
+      <c r="Q424">
+        <v>5</v>
+      </c>
+      <c r="R424">
+        <v>8</v>
+      </c>
+      <c r="S424">
+        <v>0</v>
+      </c>
+      <c r="T424">
+        <v>7</v>
+      </c>
+      <c r="U424">
+        <v>0</v>
+      </c>
+      <c r="V424">
+        <v>0</v>
+      </c>
+      <c r="W424">
+        <v>0</v>
+      </c>
+      <c r="X424">
+        <v>0</v>
+      </c>
+      <c r="Y424">
+        <v>0</v>
+      </c>
+      <c r="Z424">
+        <v>0</v>
+      </c>
+      <c r="AA424">
+        <v>0</v>
+      </c>
+      <c r="AB424">
+        <v>0</v>
+      </c>
+      <c r="AC424">
+        <v>0</v>
+      </c>
+      <c r="AD424">
+        <v>0</v>
+      </c>
+      <c r="AE424">
+        <v>0</v>
+      </c>
+      <c r="AF424">
+        <v>0</v>
+      </c>
+      <c r="AG424">
+        <v>0</v>
+      </c>
+      <c r="AH424">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A425">
+        <v>2026</v>
+      </c>
+      <c r="B425" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C425">
+        <v>21</v>
+      </c>
+      <c r="D425" t="s">
+        <v>76</v>
+      </c>
+      <c r="E425" t="str">
+        <f>VLOOKUP(D425,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F425" t="s">
+        <v>12</v>
+      </c>
+      <c r="G425">
+        <v>8</v>
+      </c>
+      <c r="H425">
+        <v>3</v>
+      </c>
+      <c r="I425">
+        <v>3</v>
+      </c>
+      <c r="J425" t="s">
+        <v>37</v>
+      </c>
+      <c r="K425" t="s">
+        <v>31</v>
+      </c>
+      <c r="L425">
+        <f t="shared" si="9"/>
+        <v>34</v>
+      </c>
+      <c r="M425">
+        <v>6</v>
+      </c>
+      <c r="N425">
+        <v>5</v>
+      </c>
+      <c r="O425">
+        <v>5</v>
+      </c>
+      <c r="P425">
+        <v>6</v>
+      </c>
+      <c r="Q425">
+        <v>5</v>
+      </c>
+      <c r="R425">
+        <v>8</v>
+      </c>
+      <c r="S425">
+        <v>5</v>
+      </c>
+      <c r="T425">
+        <v>0</v>
+      </c>
+      <c r="U425">
+        <v>5</v>
+      </c>
+      <c r="V425">
+        <v>0</v>
+      </c>
+      <c r="W425">
+        <v>0</v>
+      </c>
+      <c r="X425">
+        <v>0</v>
+      </c>
+      <c r="Y425">
+        <v>0</v>
+      </c>
+      <c r="Z425">
+        <v>0</v>
+      </c>
+      <c r="AA425">
+        <v>0</v>
+      </c>
+      <c r="AB425">
+        <v>0</v>
+      </c>
+      <c r="AC425">
+        <v>0</v>
+      </c>
+      <c r="AD425">
+        <v>0</v>
+      </c>
+      <c r="AE425">
+        <v>0</v>
+      </c>
+      <c r="AF425">
+        <v>0</v>
+      </c>
+      <c r="AG425">
+        <v>0</v>
+      </c>
+      <c r="AH425">
         <v>0</v>
       </c>
     </row>

--- a/catan_data.xlsx
+++ b/catan_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88b1f18c208c1b3c/Documents/CatanData/catan_data/catan_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1983" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FBB7069-6753-481C-A382-73F6147AB879}"/>
+  <xr:revisionPtr revIDLastSave="2074" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0011640C-E5D0-4E78-BD27-DC0DA11325F0}"/>
   <bookViews>
     <workbookView xWindow="10" yWindow="10" windowWidth="22540" windowHeight="15020" xr2:uid="{83B30B11-FE95-4925-9DB4-CCB67C570BD6}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="79">
   <si>
     <t>season</t>
   </si>
@@ -656,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}">
-  <dimension ref="A1:AP425"/>
+  <dimension ref="A1:AP428"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -38860,7 +38860,7 @@
         <v>31</v>
       </c>
       <c r="L366">
-        <f t="shared" ref="L366:L425" si="9">SUM(O366:V366)</f>
+        <f t="shared" ref="L366:L428" si="9">SUM(O366:V366)</f>
         <v>33</v>
       </c>
       <c r="M366">
@@ -45181,6 +45181,324 @@
         <v>0</v>
       </c>
       <c r="AH425">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A426">
+        <v>2026</v>
+      </c>
+      <c r="B426" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C426">
+        <v>22</v>
+      </c>
+      <c r="D426" t="s">
+        <v>76</v>
+      </c>
+      <c r="E426" t="str">
+        <f>VLOOKUP(D426,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F426" t="s">
+        <v>11</v>
+      </c>
+      <c r="G426">
+        <v>8</v>
+      </c>
+      <c r="H426">
+        <v>1</v>
+      </c>
+      <c r="I426">
+        <v>3</v>
+      </c>
+      <c r="J426" t="s">
+        <v>36</v>
+      </c>
+      <c r="K426" t="s">
+        <v>31</v>
+      </c>
+      <c r="L426">
+        <f t="shared" si="9"/>
+        <v>26</v>
+      </c>
+      <c r="M426">
+        <v>5</v>
+      </c>
+      <c r="N426">
+        <v>5</v>
+      </c>
+      <c r="O426">
+        <v>1</v>
+      </c>
+      <c r="P426">
+        <v>10</v>
+      </c>
+      <c r="Q426">
+        <v>1</v>
+      </c>
+      <c r="R426">
+        <v>8</v>
+      </c>
+      <c r="S426">
+        <v>5</v>
+      </c>
+      <c r="T426">
+        <v>0</v>
+      </c>
+      <c r="U426">
+        <v>0</v>
+      </c>
+      <c r="V426">
+        <v>1</v>
+      </c>
+      <c r="W426">
+        <v>0</v>
+      </c>
+      <c r="X426">
+        <v>0</v>
+      </c>
+      <c r="Y426">
+        <v>0</v>
+      </c>
+      <c r="Z426">
+        <v>0</v>
+      </c>
+      <c r="AA426">
+        <v>0</v>
+      </c>
+      <c r="AB426">
+        <v>0</v>
+      </c>
+      <c r="AC426">
+        <v>0</v>
+      </c>
+      <c r="AD426">
+        <v>0</v>
+      </c>
+      <c r="AE426">
+        <v>0</v>
+      </c>
+      <c r="AF426">
+        <v>0</v>
+      </c>
+      <c r="AG426">
+        <v>1</v>
+      </c>
+      <c r="AH426">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A427">
+        <v>2026</v>
+      </c>
+      <c r="B427" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C427">
+        <v>22</v>
+      </c>
+      <c r="D427" t="s">
+        <v>76</v>
+      </c>
+      <c r="E427" t="str">
+        <f>VLOOKUP(D427,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F427" t="s">
+        <v>13</v>
+      </c>
+      <c r="G427">
+        <v>13</v>
+      </c>
+      <c r="H427">
+        <v>6</v>
+      </c>
+      <c r="I427">
+        <v>1</v>
+      </c>
+      <c r="J427" t="s">
+        <v>32</v>
+      </c>
+      <c r="K427" t="s">
+        <v>31</v>
+      </c>
+      <c r="L427">
+        <f t="shared" si="9"/>
+        <v>32</v>
+      </c>
+      <c r="M427">
+        <v>5</v>
+      </c>
+      <c r="N427">
+        <v>5</v>
+      </c>
+      <c r="O427">
+        <v>10</v>
+      </c>
+      <c r="P427">
+        <v>3</v>
+      </c>
+      <c r="Q427">
+        <v>3</v>
+      </c>
+      <c r="R427">
+        <v>4</v>
+      </c>
+      <c r="S427">
+        <v>2</v>
+      </c>
+      <c r="T427">
+        <v>5</v>
+      </c>
+      <c r="U427">
+        <v>2</v>
+      </c>
+      <c r="V427">
+        <v>3</v>
+      </c>
+      <c r="W427">
+        <v>0</v>
+      </c>
+      <c r="X427">
+        <v>0</v>
+      </c>
+      <c r="Y427">
+        <v>0</v>
+      </c>
+      <c r="Z427">
+        <v>0</v>
+      </c>
+      <c r="AA427">
+        <v>0</v>
+      </c>
+      <c r="AB427">
+        <v>0</v>
+      </c>
+      <c r="AC427">
+        <v>1</v>
+      </c>
+      <c r="AD427">
+        <v>0</v>
+      </c>
+      <c r="AE427">
+        <v>0</v>
+      </c>
+      <c r="AF427">
+        <v>0</v>
+      </c>
+      <c r="AG427">
+        <v>0</v>
+      </c>
+      <c r="AH427">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A428">
+        <v>2026</v>
+      </c>
+      <c r="B428" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C428">
+        <v>22</v>
+      </c>
+      <c r="D428" t="s">
+        <v>76</v>
+      </c>
+      <c r="E428" t="str">
+        <f>VLOOKUP(D428,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F428" t="s">
+        <v>12</v>
+      </c>
+      <c r="G428">
+        <v>9</v>
+      </c>
+      <c r="H428">
+        <v>3</v>
+      </c>
+      <c r="I428">
+        <v>2</v>
+      </c>
+      <c r="J428" t="s">
+        <v>37</v>
+      </c>
+      <c r="K428" t="s">
+        <v>31</v>
+      </c>
+      <c r="L428">
+        <f t="shared" si="9"/>
+        <v>38</v>
+      </c>
+      <c r="M428">
+        <v>5</v>
+      </c>
+      <c r="N428">
+        <v>4</v>
+      </c>
+      <c r="O428">
+        <v>12</v>
+      </c>
+      <c r="P428">
+        <v>10</v>
+      </c>
+      <c r="Q428">
+        <v>3</v>
+      </c>
+      <c r="R428">
+        <v>5</v>
+      </c>
+      <c r="S428">
+        <v>0</v>
+      </c>
+      <c r="T428">
+        <v>8</v>
+      </c>
+      <c r="U428">
+        <v>0</v>
+      </c>
+      <c r="V428">
+        <v>0</v>
+      </c>
+      <c r="W428">
+        <v>0</v>
+      </c>
+      <c r="X428">
+        <v>0</v>
+      </c>
+      <c r="Y428">
+        <v>0</v>
+      </c>
+      <c r="Z428">
+        <v>0</v>
+      </c>
+      <c r="AA428">
+        <v>0</v>
+      </c>
+      <c r="AB428">
+        <v>0</v>
+      </c>
+      <c r="AC428">
+        <v>0</v>
+      </c>
+      <c r="AD428">
+        <v>0</v>
+      </c>
+      <c r="AE428">
+        <v>1</v>
+      </c>
+      <c r="AF428">
+        <v>0</v>
+      </c>
+      <c r="AG428">
+        <v>0</v>
+      </c>
+      <c r="AH428">
         <v>0</v>
       </c>
     </row>

--- a/catan_data.xlsx
+++ b/catan_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88b1f18c208c1b3c/Documents/CatanData/catan_data/catan_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2074" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0011640C-E5D0-4E78-BD27-DC0DA11325F0}"/>
+  <xr:revisionPtr revIDLastSave="2170" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D69007BD-92F3-46D6-97CD-EDFA77890DD0}"/>
   <bookViews>
     <workbookView xWindow="10" yWindow="10" windowWidth="22540" windowHeight="15020" xr2:uid="{83B30B11-FE95-4925-9DB4-CCB67C570BD6}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="79">
   <si>
     <t>season</t>
   </si>
@@ -656,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}">
-  <dimension ref="A1:AP428"/>
+  <dimension ref="A1:AP431"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -38860,7 +38860,7 @@
         <v>31</v>
       </c>
       <c r="L366">
-        <f t="shared" ref="L366:L428" si="9">SUM(O366:V366)</f>
+        <f t="shared" ref="L366:L429" si="9">SUM(O366:V366)</f>
         <v>33</v>
       </c>
       <c r="M366">
@@ -45499,6 +45499,324 @@
         <v>0</v>
       </c>
       <c r="AH428">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A429">
+        <v>2026</v>
+      </c>
+      <c r="B429" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C429">
+        <v>23</v>
+      </c>
+      <c r="D429" t="s">
+        <v>76</v>
+      </c>
+      <c r="E429" t="str">
+        <f>VLOOKUP(D429,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F429" t="s">
+        <v>13</v>
+      </c>
+      <c r="G429">
+        <v>9</v>
+      </c>
+      <c r="H429">
+        <v>5</v>
+      </c>
+      <c r="I429">
+        <v>2</v>
+      </c>
+      <c r="J429" t="s">
+        <v>36</v>
+      </c>
+      <c r="K429" t="s">
+        <v>31</v>
+      </c>
+      <c r="L429">
+        <f t="shared" si="9"/>
+        <v>23</v>
+      </c>
+      <c r="M429">
+        <v>6</v>
+      </c>
+      <c r="N429">
+        <v>4</v>
+      </c>
+      <c r="O429">
+        <v>4</v>
+      </c>
+      <c r="P429">
+        <v>0</v>
+      </c>
+      <c r="Q429">
+        <v>5</v>
+      </c>
+      <c r="R429">
+        <v>2</v>
+      </c>
+      <c r="S429">
+        <v>5</v>
+      </c>
+      <c r="T429">
+        <v>0</v>
+      </c>
+      <c r="U429">
+        <v>0</v>
+      </c>
+      <c r="V429">
+        <v>7</v>
+      </c>
+      <c r="W429">
+        <v>0</v>
+      </c>
+      <c r="X429">
+        <v>0</v>
+      </c>
+      <c r="Y429">
+        <v>0</v>
+      </c>
+      <c r="Z429">
+        <v>0</v>
+      </c>
+      <c r="AA429">
+        <v>0</v>
+      </c>
+      <c r="AB429">
+        <v>0</v>
+      </c>
+      <c r="AC429">
+        <v>1</v>
+      </c>
+      <c r="AD429">
+        <v>0</v>
+      </c>
+      <c r="AE429">
+        <v>0</v>
+      </c>
+      <c r="AF429">
+        <v>0</v>
+      </c>
+      <c r="AG429">
+        <v>0</v>
+      </c>
+      <c r="AH429">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="430" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A430">
+        <v>2026</v>
+      </c>
+      <c r="B430" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C430">
+        <v>23</v>
+      </c>
+      <c r="D430" t="s">
+        <v>76</v>
+      </c>
+      <c r="E430" t="str">
+        <f>VLOOKUP(D430,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F430" t="s">
+        <v>11</v>
+      </c>
+      <c r="G430">
+        <v>13</v>
+      </c>
+      <c r="H430">
+        <v>6</v>
+      </c>
+      <c r="I430">
+        <v>1</v>
+      </c>
+      <c r="J430" t="s">
+        <v>32</v>
+      </c>
+      <c r="K430" t="s">
+        <v>31</v>
+      </c>
+      <c r="L430">
+        <f t="shared" ref="L430:L431" si="10">SUM(O430:V430)</f>
+        <v>36</v>
+      </c>
+      <c r="M430">
+        <v>6</v>
+      </c>
+      <c r="N430">
+        <v>4</v>
+      </c>
+      <c r="O430">
+        <v>7</v>
+      </c>
+      <c r="P430">
+        <v>0</v>
+      </c>
+      <c r="Q430">
+        <v>5</v>
+      </c>
+      <c r="R430">
+        <v>7</v>
+      </c>
+      <c r="S430">
+        <v>9</v>
+      </c>
+      <c r="T430">
+        <v>3</v>
+      </c>
+      <c r="U430">
+        <v>5</v>
+      </c>
+      <c r="V430">
+        <v>0</v>
+      </c>
+      <c r="W430">
+        <v>0</v>
+      </c>
+      <c r="X430">
+        <v>0</v>
+      </c>
+      <c r="Y430">
+        <v>0</v>
+      </c>
+      <c r="Z430">
+        <v>0</v>
+      </c>
+      <c r="AA430">
+        <v>0</v>
+      </c>
+      <c r="AB430">
+        <v>0</v>
+      </c>
+      <c r="AC430">
+        <v>0</v>
+      </c>
+      <c r="AD430">
+        <v>0</v>
+      </c>
+      <c r="AE430">
+        <v>0</v>
+      </c>
+      <c r="AF430">
+        <v>0</v>
+      </c>
+      <c r="AG430">
+        <v>1</v>
+      </c>
+      <c r="AH430">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="431" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A431">
+        <v>2026</v>
+      </c>
+      <c r="B431" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C431">
+        <v>23</v>
+      </c>
+      <c r="D431" t="s">
+        <v>76</v>
+      </c>
+      <c r="E431" t="str">
+        <f>VLOOKUP(D431,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F431" t="s">
+        <v>12</v>
+      </c>
+      <c r="G431">
+        <v>7</v>
+      </c>
+      <c r="H431">
+        <v>0</v>
+      </c>
+      <c r="I431">
+        <v>3</v>
+      </c>
+      <c r="J431" t="s">
+        <v>37</v>
+      </c>
+      <c r="K431" t="s">
+        <v>31</v>
+      </c>
+      <c r="L431">
+        <f t="shared" si="10"/>
+        <v>31</v>
+      </c>
+      <c r="M431">
+        <v>5</v>
+      </c>
+      <c r="N431">
+        <v>5</v>
+      </c>
+      <c r="O431">
+        <v>3</v>
+      </c>
+      <c r="P431">
+        <v>5</v>
+      </c>
+      <c r="Q431">
+        <v>4</v>
+      </c>
+      <c r="R431">
+        <v>6</v>
+      </c>
+      <c r="S431">
+        <v>5</v>
+      </c>
+      <c r="T431">
+        <v>3</v>
+      </c>
+      <c r="U431">
+        <v>5</v>
+      </c>
+      <c r="V431">
+        <v>0</v>
+      </c>
+      <c r="W431">
+        <v>0</v>
+      </c>
+      <c r="X431">
+        <v>0</v>
+      </c>
+      <c r="Y431">
+        <v>0</v>
+      </c>
+      <c r="Z431">
+        <v>0</v>
+      </c>
+      <c r="AA431">
+        <v>0</v>
+      </c>
+      <c r="AB431">
+        <v>0</v>
+      </c>
+      <c r="AC431">
+        <v>0</v>
+      </c>
+      <c r="AD431">
+        <v>1</v>
+      </c>
+      <c r="AE431">
+        <v>0</v>
+      </c>
+      <c r="AF431">
+        <v>0</v>
+      </c>
+      <c r="AG431">
+        <v>0</v>
+      </c>
+      <c r="AH431">
         <v>0</v>
       </c>
     </row>
